--- a/tests/DCR-JackReacher.xlsx
+++ b/tests/DCR-JackReacher.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mc142/Documents/workspace/mortality-reporting/mdi-import/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A90F01-8BCD-3845-BEB7-4715C7C225A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30E75BC-640A-AD4D-B602-2A19CA8651C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2840" yWindow="680" windowWidth="26220" windowHeight="20660" xr2:uid="{7A50F290-1C75-487E-9806-F93553E4E7CC}"/>
   </bookViews>
@@ -26,8 +26,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="253">
   <si>
     <t>Sections</t>
   </si>
@@ -1016,6 +1038,12 @@
   <si>
     <t>Jack Reacher</t>
   </si>
+  <si>
+    <t>Funeral Home: Signature</t>
+  </si>
+  <si>
+    <t>Signature in image</t>
+  </si>
 </sst>
 </file>
 
@@ -1025,7 +1053,7 @@
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="[&lt;=9999999]###\-####;\(###\)\ ###\-####"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1111,6 +1139,14 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="26">
@@ -1368,7 +1404,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -1895,6 +1931,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1930,6 +1972,70 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2229,7 +2335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54CD1DC7-E143-4CF5-BEA9-4DABBAFFC7B0}">
-  <dimension ref="A1:AU88"/>
+  <dimension ref="A1:AU89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="21" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.33203125" style="46" customWidth="1"/>
@@ -3747,6 +3853,23 @@
       <c r="G88" s="166"/>
       <c r="H88" s="166"/>
       <c r="I88" s="167"/>
+    </row>
+    <row r="89" spans="1:9" s="168" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="163"/>
+      <c r="B89" s="170" t="s">
+        <v>251</v>
+      </c>
+      <c r="C89" s="165" t="s">
+        <v>252</v>
+      </c>
+      <c r="D89" s="171" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E89" s="166"/>
+      <c r="F89" s="166"/>
+      <c r="G89" s="166"/>
+      <c r="H89" s="166"/>
+      <c r="I89" s="167"/>
     </row>
   </sheetData>
   <sheetProtection deleteColumns="0" selectLockedCells="1"/>
@@ -4410,20 +4533,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">YVWEJ5DVYS2U-421999773-68</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">
-      <Url>https://cdcpartners.sharepoint.com/sites/NCHS/nvssmodcop/_layouts/15/DocIdRedir.aspx?ID=YVWEJ5DVYS2U-421999773-68</Url>
-      <Description>YVWEJ5DVYS2U-421999773-68</Description>
-    </_dlc_DocIdUrl>
-    <ShareFileCreator xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
-    <ShareFileCreated xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008D4902BA52C7D94A994657A564808B2B" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e4455a60d2ff5f5fcd8815d6d89b5b66">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b541edd5-2552-480e-ada6-0e2c8d317108" xmlns:ns3="780ae317-08c5-4e10-af93-dd385a8384a9" xmlns:ns4="3146657c-56f4-4c0a-bb9c-a675121ac670" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1d01ecd782f081d5d944fa263943fc4" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="b541edd5-2552-480e-ada6-0e2c8d317108"/>
@@ -4622,7 +4731,30 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">YVWEJ5DVYS2U-421999773-68</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">
+      <Url>https://cdcpartners.sharepoint.com/sites/NCHS/nvssmodcop/_layouts/15/DocIdRedir.aspx?ID=YVWEJ5DVYS2U-421999773-68</Url>
+      <Description>YVWEJ5DVYS2U-421999773-68</Description>
+    </_dlc_DocIdUrl>
+    <ShareFileCreator xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
+    <ShareFileCreated xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -4672,34 +4804,7 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E3EF86-6C9E-4C22-A476-13DA012C68C5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="780ae317-08c5-4e10-af93-dd385a8384a9"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="b541edd5-2552-480e-ada6-0e2c8d317108"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3146657c-56f4-4c0a-bb9c-a675121ac670"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0980278E-2A79-4F44-8623-FE545C304BE1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4719,18 +4824,36 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E3EF86-6C9E-4C22-A476-13DA012C68C5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="780ae317-08c5-4e10-af93-dd385a8384a9"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="b541edd5-2552-480e-ada6-0e2c8d317108"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3146657c-56f4-4c0a-bb9c-a675121ac670"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{448710E8-BE9E-4C9E-A40A-0AC1DAE48E99}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF0D7A6D-D78F-4048-9348-0B4289842B11}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{448710E8-BE9E-4C9E-A40A-0AC1DAE48E99}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/tests/DCR-JackReacher.xlsx
+++ b/tests/DCR-JackReacher.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mc142/Documents/workspace/mortality-reporting/mdi-import/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30E75BC-640A-AD4D-B602-2A19CA8651C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77AFE81-F81C-5E4D-B880-C87377331BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2840" yWindow="680" windowWidth="26220" windowHeight="20660" xr2:uid="{7A50F290-1C75-487E-9806-F93553E4E7CC}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="256">
   <si>
     <t>Sections</t>
   </si>
@@ -919,9 +919,6 @@
     <t>GA</t>
   </si>
   <si>
-    <t>MDI-DEV-GOLDENSET-HanSolo-DCR</t>
-  </si>
-  <si>
     <t>Location of Injury: Street</t>
   </si>
   <si>
@@ -1043,6 +1040,18 @@
   </si>
   <si>
     <t>Signature in image</t>
+  </si>
+  <si>
+    <t>Funeral Home: Director Name</t>
+  </si>
+  <si>
+    <t>Funeral Home Director (or Authorized) Name who is authoritative person for the DCR request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">William Shakespeare </t>
+  </si>
+  <si>
+    <t>MDI-DEV-GOLDENSET-JackReacher-DCR</t>
   </si>
 </sst>
 </file>
@@ -2335,7 +2344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54CD1DC7-E143-4CF5-BEA9-4DABBAFFC7B0}">
-  <dimension ref="A1:AU89"/>
+  <dimension ref="A1:AU90"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="21" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.33203125" style="46" customWidth="1"/>
@@ -2385,7 +2394,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="95" t="s">
-        <v>212</v>
+        <v>255</v>
       </c>
       <c r="C3" s="96" t="s">
         <v>10</v>
@@ -2460,7 +2469,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="138" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
@@ -2528,7 +2537,7 @@
         <v>31</v>
       </c>
       <c r="D12" s="138" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
@@ -3000,7 +3009,7 @@
       </c>
       <c r="C44" s="83"/>
       <c r="D44" s="155" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E44" s="26"/>
       <c r="F44" s="26"/>
@@ -3011,13 +3020,13 @@
     <row r="45" spans="1:9" s="28" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A45" s="53"/>
       <c r="B45" s="71" t="s">
+        <v>212</v>
+      </c>
+      <c r="C45" s="83" t="s">
         <v>213</v>
       </c>
-      <c r="C45" s="83" t="s">
-        <v>214</v>
-      </c>
       <c r="D45" s="149" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E45" s="156"/>
       <c r="F45" s="26"/>
@@ -3028,11 +3037,11 @@
     <row r="46" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="53"/>
       <c r="B46" s="71" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C46" s="83"/>
       <c r="D46" s="149" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E46" s="156"/>
       <c r="F46" s="26"/>
@@ -3043,7 +3052,7 @@
     <row r="47" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="53"/>
       <c r="B47" s="71" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C47" s="83"/>
       <c r="D47" s="149"/>
@@ -3056,7 +3065,7 @@
     <row r="48" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="53"/>
       <c r="B48" s="71" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C48" s="83"/>
       <c r="D48" s="149" t="s">
@@ -3071,7 +3080,7 @@
     <row r="49" spans="1:47" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="53"/>
       <c r="B49" s="71" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C49" s="83"/>
       <c r="D49" s="149">
@@ -3086,7 +3095,7 @@
     <row r="50" spans="1:47" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="53"/>
       <c r="B50" s="71" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C50" s="83"/>
       <c r="D50" s="149"/>
@@ -3643,7 +3652,7 @@
         <v>120</v>
       </c>
       <c r="D75" s="152" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E75" s="43"/>
       <c r="F75" s="43"/>
@@ -3654,13 +3663,13 @@
     <row r="76" spans="1:47" s="45" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A76" s="57"/>
       <c r="B76" s="74" t="s">
+        <v>225</v>
+      </c>
+      <c r="C76" s="88" t="s">
         <v>226</v>
       </c>
-      <c r="C76" s="88" t="s">
-        <v>227</v>
-      </c>
       <c r="D76" s="152" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E76" s="43"/>
       <c r="F76" s="43"/>
@@ -3671,10 +3680,10 @@
     <row r="77" spans="1:47" s="45" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A77" s="57"/>
       <c r="B77" s="74" t="s">
+        <v>227</v>
+      </c>
+      <c r="C77" s="88" t="s">
         <v>228</v>
-      </c>
-      <c r="C77" s="88" t="s">
-        <v>229</v>
       </c>
       <c r="D77" s="152">
         <v>7890123456</v>
@@ -3688,10 +3697,10 @@
     <row r="78" spans="1:47" s="45" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="57"/>
       <c r="B78" s="74" t="s">
+        <v>229</v>
+      </c>
+      <c r="C78" s="88" t="s">
         <v>230</v>
-      </c>
-      <c r="C78" s="88" t="s">
-        <v>231</v>
       </c>
       <c r="D78" s="157">
         <v>45340</v>
@@ -3711,7 +3720,7 @@
         <v>122</v>
       </c>
       <c r="D79" s="152" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E79" s="43"/>
       <c r="F79" s="43"/>
@@ -3721,7 +3730,7 @@
     </row>
     <row r="80" spans="1:47" s="162" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A80" s="158" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B80" s="159"/>
       <c r="C80" s="160"/>
@@ -3735,13 +3744,13 @@
     <row r="81" spans="1:9" s="168" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A81" s="163"/>
       <c r="B81" s="164" t="s">
+        <v>235</v>
+      </c>
+      <c r="C81" s="165" t="s">
         <v>236</v>
       </c>
-      <c r="C81" s="165" t="s">
-        <v>237</v>
-      </c>
       <c r="D81" s="166" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E81" s="166"/>
       <c r="F81" s="166"/>
@@ -3749,14 +3758,16 @@
       <c r="H81" s="166"/>
       <c r="I81" s="167"/>
     </row>
-    <row r="82" spans="1:9" s="168" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" s="168" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A82" s="163"/>
       <c r="B82" s="164" t="s">
-        <v>246</v>
-      </c>
-      <c r="C82" s="165"/>
+        <v>252</v>
+      </c>
+      <c r="C82" s="165" t="s">
+        <v>253</v>
+      </c>
       <c r="D82" s="166" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="E82" s="166"/>
       <c r="F82" s="166"/>
@@ -3767,11 +3778,11 @@
     <row r="83" spans="1:9" s="168" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A83" s="163"/>
       <c r="B83" s="164" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C83" s="165"/>
       <c r="D83" s="166" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E83" s="166"/>
       <c r="F83" s="166"/>
@@ -3782,11 +3793,11 @@
     <row r="84" spans="1:9" s="168" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A84" s="163"/>
       <c r="B84" s="164" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C84" s="165"/>
       <c r="D84" s="166" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E84" s="166"/>
       <c r="F84" s="166"/>
@@ -3797,11 +3808,11 @@
     <row r="85" spans="1:9" s="168" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="163"/>
       <c r="B85" s="164" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C85" s="165"/>
       <c r="D85" s="166" t="s">
-        <v>210</v>
+        <v>243</v>
       </c>
       <c r="E85" s="166"/>
       <c r="F85" s="166"/>
@@ -3812,11 +3823,11 @@
     <row r="86" spans="1:9" s="168" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="163"/>
       <c r="B86" s="164" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C86" s="165"/>
       <c r="D86" s="166" t="s">
-        <v>245</v>
+        <v>210</v>
       </c>
       <c r="E86" s="166"/>
       <c r="F86" s="166"/>
@@ -3824,14 +3835,14 @@
       <c r="H86" s="166"/>
       <c r="I86" s="167"/>
     </row>
-    <row r="87" spans="1:9" s="168" customFormat="1" ht="31" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" s="168" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="163"/>
-      <c r="B87" s="169" t="s">
-        <v>241</v>
+      <c r="B87" s="164" t="s">
+        <v>239</v>
       </c>
       <c r="C87" s="165"/>
       <c r="D87" s="166" t="s">
-        <v>211</v>
+        <v>244</v>
       </c>
       <c r="E87" s="166"/>
       <c r="F87" s="166"/>
@@ -3839,14 +3850,14 @@
       <c r="H87" s="166"/>
       <c r="I87" s="167"/>
     </row>
-    <row r="88" spans="1:9" s="168" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" s="168" customFormat="1" ht="31" x14ac:dyDescent="0.3">
       <c r="A88" s="163"/>
-      <c r="B88" s="164" t="s">
-        <v>242</v>
+      <c r="B88" s="169" t="s">
+        <v>240</v>
       </c>
       <c r="C88" s="165"/>
-      <c r="D88" s="166">
-        <v>10203</v>
+      <c r="D88" s="166" t="s">
+        <v>211</v>
       </c>
       <c r="E88" s="166"/>
       <c r="F88" s="166"/>
@@ -3856,20 +3867,35 @@
     </row>
     <row r="89" spans="1:9" s="168" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="163"/>
-      <c r="B89" s="170" t="s">
-        <v>251</v>
-      </c>
-      <c r="C89" s="165" t="s">
-        <v>252</v>
-      </c>
-      <c r="D89" s="171" t="e" vm="1">
-        <v>#VALUE!</v>
+      <c r="B89" s="164" t="s">
+        <v>241</v>
+      </c>
+      <c r="C89" s="165"/>
+      <c r="D89" s="166">
+        <v>10203</v>
       </c>
       <c r="E89" s="166"/>
       <c r="F89" s="166"/>
       <c r="G89" s="166"/>
       <c r="H89" s="166"/>
       <c r="I89" s="167"/>
+    </row>
+    <row r="90" spans="1:9" s="168" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="163"/>
+      <c r="B90" s="170" t="s">
+        <v>250</v>
+      </c>
+      <c r="C90" s="165" t="s">
+        <v>251</v>
+      </c>
+      <c r="D90" s="171" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E90" s="166"/>
+      <c r="F90" s="166"/>
+      <c r="G90" s="166"/>
+      <c r="H90" s="166"/>
+      <c r="I90" s="167"/>
     </row>
   </sheetData>
   <sheetProtection deleteColumns="0" selectLockedCells="1"/>
@@ -4357,7 +4383,7 @@
         <v>136</v>
       </c>
       <c r="M2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N2" t="s">
         <v>188</v>
@@ -4401,7 +4427,7 @@
         <v>142</v>
       </c>
       <c r="M3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="N3" t="s">
         <v>189</v>
@@ -4445,7 +4471,7 @@
         <v>152</v>
       </c>
       <c r="M4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N4" t="s">
         <v>190</v>
@@ -4533,6 +4559,79 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">YVWEJ5DVYS2U-421999773-68</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">
+      <Url>https://cdcpartners.sharepoint.com/sites/NCHS/nvssmodcop/_layouts/15/DocIdRedir.aspx?ID=YVWEJ5DVYS2U-421999773-68</Url>
+      <Description>YVWEJ5DVYS2U-421999773-68</Description>
+    </_dlc_DocIdUrl>
+    <ShareFileCreator xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
+    <ShareFileCreated xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008D4902BA52C7D94A994657A564808B2B" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e4455a60d2ff5f5fcd8815d6d89b5b66">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b541edd5-2552-480e-ada6-0e2c8d317108" xmlns:ns3="780ae317-08c5-4e10-af93-dd385a8384a9" xmlns:ns4="3146657c-56f4-4c0a-bb9c-a675121ac670" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1d01ecd782f081d5d944fa263943fc4" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="b541edd5-2552-480e-ada6-0e2c8d317108"/>
@@ -4731,80 +4830,41 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">YVWEJ5DVYS2U-421999773-68</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">
-      <Url>https://cdcpartners.sharepoint.com/sites/NCHS/nvssmodcop/_layouts/15/DocIdRedir.aspx?ID=YVWEJ5DVYS2U-421999773-68</Url>
-      <Description>YVWEJ5DVYS2U-421999773-68</Description>
-    </_dlc_DocIdUrl>
-    <ShareFileCreator xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
-    <ShareFileCreated xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E3EF86-6C9E-4C22-A476-13DA012C68C5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="780ae317-08c5-4e10-af93-dd385a8384a9"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="b541edd5-2552-480e-ada6-0e2c8d317108"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3146657c-56f4-4c0a-bb9c-a675121ac670"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{448710E8-BE9E-4C9E-A40A-0AC1DAE48E99}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF0D7A6D-D78F-4048-9348-0B4289842B11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0980278E-2A79-4F44-8623-FE545C304BE1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4822,38 +4882,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E3EF86-6C9E-4C22-A476-13DA012C68C5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="780ae317-08c5-4e10-af93-dd385a8384a9"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="b541edd5-2552-480e-ada6-0e2c8d317108"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3146657c-56f4-4c0a-bb9c-a675121ac670"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{448710E8-BE9E-4C9E-A40A-0AC1DAE48E99}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF0D7A6D-D78F-4048-9348-0B4289842B11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/tests/DCR-JackReacher.xlsx
+++ b/tests/DCR-JackReacher.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mc142/Documents/workspace/mortality-reporting/mdi-import/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77AFE81-F81C-5E4D-B880-C87377331BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069BD54D-DEB1-6548-9CAD-3016E27376C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2840" yWindow="680" windowWidth="26220" windowHeight="20660" xr2:uid="{7A50F290-1C75-487E-9806-F93553E4E7CC}"/>
+    <workbookView xWindow="8340" yWindow="1040" windowWidth="33600" windowHeight="20660" xr2:uid="{7A50F290-1C75-487E-9806-F93553E4E7CC}"/>
   </bookViews>
   <sheets>
-    <sheet name="Base Input Schema" sheetId="4" r:id="rId1"/>
-    <sheet name="DCR Extension Input Schema" sheetId="6" r:id="rId2"/>
-    <sheet name="Drop Down List Values" sheetId="5" r:id="rId3"/>
+    <sheet name="DCR" sheetId="4" r:id="rId1"/>
+    <sheet name="Drop Down List Values" sheetId="5" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -49,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="236">
   <si>
     <t>Sections</t>
   </si>
@@ -647,203 +646,6 @@
     <t>Medical Examiner</t>
   </si>
   <si>
-    <t>This Excel File can be imported into RAVEN2.0; converting into FHIR and importing into RAVEN. This tab describes the DCR specific data need for a Death Certificate Review, extending upon the "Base Input Schema"</t>
-  </si>
-  <si>
-    <t>Message Info</t>
-  </si>
-  <si>
-    <t>Submittor Name</t>
-  </si>
-  <si>
-    <t>Submittor Email</t>
-  </si>
-  <si>
-    <t>Name of the person who is submitting the Death Certificate Review Message
-Accepted Formats:
-&lt;First Name&gt; &lt;Last Name&gt;
-&lt;First Name&gt; &lt;Middle Initial&gt; &lt;Last Name&gt;
-&lt;First Name&gt; &lt;Middle Name&gt; &lt;Last Name&gt;</t>
-  </si>
-  <si>
-    <t>Email Addres of the person who is submitting the Death Certificate Review Message
-Accepted Formats:
-&lt;address&gt;@&lt;domain&gt;</t>
-  </si>
-  <si>
-    <t>Funeral Home</t>
-  </si>
-  <si>
-    <t>Funeral Home Name</t>
-  </si>
-  <si>
-    <t>This section is for The Funeral Home which admitted the body</t>
-  </si>
-  <si>
-    <t>Name of the admitting funeral home</t>
-  </si>
-  <si>
-    <t>Funeral Home Address: Street</t>
-  </si>
-  <si>
-    <t>Funeral Home Address: city</t>
-  </si>
-  <si>
-    <t>Funeral Home Address: county</t>
-  </si>
-  <si>
-    <t>Funeral Home Address: State, U.S. Territory or Canadian Province</t>
-  </si>
-  <si>
-    <t>Funeral Home Address: Postal Code</t>
-  </si>
-  <si>
-    <t>Funeral Home Address: Country</t>
-  </si>
-  <si>
-    <t>Primary address of the funeral home. Multiple lines are supported</t>
-  </si>
-  <si>
-    <t>Funeral Home Phone Number</t>
-  </si>
-  <si>
-    <t>Funeral Home Fax Number</t>
-  </si>
-  <si>
-    <t>Primary Contact Phone Number of Funeral Home</t>
-  </si>
-  <si>
-    <t>Primary Fax Address of Funeral Home</t>
-  </si>
-  <si>
-    <t>Message Reason</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Context for why this message is being sent. Accepted Values shown in the dropdown
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>DC_MED_DATA_Q_REQ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">	  Death Certificate Medical Data Quality Review Request
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>DC_MED_DATA_Q_RSP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">	  Death Certificate Medical Data Quality Review Response
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>DC_PER_DATA_Q_REQ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">	  Death Certificate Personal Data Quality Review Request
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>DC_PER_DATA_Q_RSP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">	  Death Certificate Personal Data Quality Review Response
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>CREM_C_REQ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">	  Cremation Clearance Request
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>CREM_C_RSP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">	  Cremation Clearance Response</t>
-    </r>
-  </si>
-  <si>
     <t>DC_MED_DATA_Q_REQ</t>
   </si>
   <si>
@@ -860,21 +662,6 @@
   </si>
   <si>
     <t>CREM_C_RSP</t>
-  </si>
-  <si>
-    <t>Submittor Fax Number</t>
-  </si>
-  <si>
-    <t>Submittor Phone Number</t>
-  </si>
-  <si>
-    <t>Primary Contact Phone Number of the person who is submitting the Death Certificate Review Message</t>
-  </si>
-  <si>
-    <t>Primary Fax Address of the person who is submitting the Death Certificate Review Message</t>
-  </si>
-  <si>
-    <t>This Excel File can be imported into RAVEN2.0; converting into FHIR and importing into RAVEN</t>
   </si>
   <si>
     <t>Decedent Residence: City</t>
@@ -1052,17 +839,40 @@
   </si>
   <si>
     <t>MDI-DEV-GOLDENSET-JackReacher-DCR</t>
+  </si>
+  <si>
+    <t>Usecase</t>
+  </si>
+  <si>
+    <t>Death Certificate Review (DCR) FHIR Profile</t>
+  </si>
+  <si>
+    <t>This Excel File can be imported into RAVEN. Mapping data in this file to Death Certificate Review (DCR) FHIR Profile</t>
+  </si>
+  <si>
+    <t>Funeral Home: Director ID System</t>
+  </si>
+  <si>
+    <t>Funeral Home Director's identifier system</t>
+  </si>
+  <si>
+    <t>Funeral Home: Director ID</t>
+  </si>
+  <si>
+    <t>Funeral Home Director's identifier value</t>
+  </si>
+  <si>
+    <t>urn:funeralhome:fulton</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
-    <numFmt numFmtId="165" formatCode="[&lt;=9999999]###\-####;\(###\)\ ###\-####"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1135,21 +945,6 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -1158,7 +953,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1267,30 +1062,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC48C00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88723C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FBA6E"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF637A3A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1405,15 +1176,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -1594,47 +1364,15 @@
     <xf numFmtId="0" fontId="6" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1696,9 +1434,6 @@
     <xf numFmtId="0" fontId="8" fillId="10" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1718,9 +1453,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1731,102 +1463,6 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="22" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="22" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="22" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="20" borderId="1" xfId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
@@ -1910,48 +1546,92 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="5">
     <cellStyle name="Bad" xfId="4" builtinId="27"/>
     <cellStyle name="Good" xfId="3" builtinId="26"/>
-    <cellStyle name="Hyperlink" xfId="5" builtinId="8"/>
     <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 4" xfId="1" xr:uid="{40ABF838-51BB-482E-A30F-1A2350126FD1}"/>
@@ -2344,12 +2024,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54CD1DC7-E143-4CF5-BEA9-4DABBAFFC7B0}">
-  <dimension ref="A1:AU90"/>
+  <dimension ref="A1:AU92"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="21" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.33203125" style="46" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="58" customWidth="1"/>
-    <col min="3" max="3" width="39.1640625" style="65" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" style="122" customWidth="1"/>
+    <col min="3" max="3" width="39.1640625" style="58" customWidth="1"/>
     <col min="4" max="8" width="32.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="8.83203125" style="1"/>
@@ -2359,10 +2039,10 @@
       <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="C1" s="58" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -2384,19 +2064,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C2" s="65" t="s">
-        <v>197</v>
+    <row r="2" spans="1:9" ht="40" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="46" t="s">
+        <v>228</v>
+      </c>
+      <c r="B2" s="122" t="s">
+        <v>229</v>
+      </c>
+      <c r="C2" s="58" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="105.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="95" t="s">
-        <v>255</v>
-      </c>
-      <c r="C3" s="96" t="s">
+      <c r="B3" s="123" t="s">
+        <v>227</v>
+      </c>
+      <c r="C3" s="81" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2404,8 +2090,8 @@
       <c r="A4" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="59"/>
-      <c r="C4" s="76" t="s">
+      <c r="B4" s="124"/>
+      <c r="C4" s="62" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="3"/>
@@ -2417,40 +2103,40 @@
     </row>
     <row r="5" spans="1:9" s="6" customFormat="1" ht="31" x14ac:dyDescent="0.3">
       <c r="A5" s="48"/>
-      <c r="B5" s="92" t="s">
+      <c r="B5" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="77" t="s">
+      <c r="C5" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="137"/>
-      <c r="E5" s="137"/>
-      <c r="F5" s="137"/>
-      <c r="G5" s="137"/>
-      <c r="H5" s="137"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
       <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:9" s="6" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A6" s="48"/>
-      <c r="B6" s="93" t="s">
+      <c r="B6" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="77" t="s">
+      <c r="C6" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="137"/>
-      <c r="E6" s="137"/>
-      <c r="F6" s="137"/>
-      <c r="G6" s="137"/>
-      <c r="H6" s="137"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90"/>
+      <c r="H6" s="90"/>
       <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" s="8" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A7" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="60"/>
-      <c r="C7" s="78" t="s">
+      <c r="B7" s="125"/>
+      <c r="C7" s="64" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="7"/>
@@ -2462,14 +2148,14 @@
     </row>
     <row r="8" spans="1:9" s="11" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A8" s="50"/>
-      <c r="B8" s="66" t="s">
+      <c r="B8" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="79" t="s">
+      <c r="C8" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="138" t="s">
-        <v>249</v>
+      <c r="D8" s="91" t="s">
+        <v>221</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
@@ -2479,13 +2165,13 @@
     </row>
     <row r="9" spans="1:9" s="11" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A9" s="50"/>
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="79" t="s">
+      <c r="C9" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="138" t="s">
+      <c r="D9" s="91" t="s">
         <v>23</v>
       </c>
       <c r="E9" s="9"/>
@@ -2496,13 +2182,13 @@
     </row>
     <row r="10" spans="1:9" s="11" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A10" s="50"/>
-      <c r="B10" s="66" t="s">
+      <c r="B10" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="79" t="s">
+      <c r="C10" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="138" t="s">
+      <c r="D10" s="91" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="9"/>
@@ -2513,13 +2199,13 @@
     </row>
     <row r="11" spans="1:9" s="11" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A11" s="50"/>
-      <c r="B11" s="67" t="s">
+      <c r="B11" s="126" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="79" t="s">
+      <c r="C11" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="138" t="s">
+      <c r="D11" s="91" t="s">
         <v>29</v>
       </c>
       <c r="E11" s="9"/>
@@ -2530,14 +2216,14 @@
     </row>
     <row r="12" spans="1:9" s="11" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A12" s="50"/>
-      <c r="B12" s="66" t="s">
+      <c r="B12" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="79" t="s">
+      <c r="C12" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="138" t="s">
-        <v>221</v>
+      <c r="D12" s="91" t="s">
+        <v>193</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
@@ -2547,13 +2233,13 @@
     </row>
     <row r="13" spans="1:9" s="11" customFormat="1" ht="65" x14ac:dyDescent="0.3">
       <c r="A13" s="50"/>
-      <c r="B13" s="66" t="s">
+      <c r="B13" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="79" t="s">
+      <c r="C13" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="138">
+      <c r="D13" s="91">
         <v>45</v>
       </c>
       <c r="E13" s="9"/>
@@ -2564,13 +2250,13 @@
     </row>
     <row r="14" spans="1:9" s="11" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A14" s="50"/>
-      <c r="B14" s="66" t="s">
+      <c r="B14" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="79" t="s">
+      <c r="C14" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="140">
+      <c r="D14" s="93">
         <v>28561</v>
       </c>
       <c r="E14" s="12"/>
@@ -2581,11 +2267,11 @@
     </row>
     <row r="15" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="50"/>
-      <c r="B15" s="66" t="s">
+      <c r="B15" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="79"/>
-      <c r="D15" s="138"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="91"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
@@ -2594,26 +2280,26 @@
     </row>
     <row r="16" spans="1:9" s="11" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A16" s="50"/>
-      <c r="B16" s="66" t="s">
+      <c r="B16" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="79" t="s">
+      <c r="C16" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="153"/>
-      <c r="E16" s="154"/>
-      <c r="F16" s="154"/>
+      <c r="D16" s="106"/>
+      <c r="E16" s="107"/>
+      <c r="F16" s="107"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
       <c r="I16" s="10"/>
     </row>
     <row r="17" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="50"/>
-      <c r="B17" s="66" t="s">
-        <v>198</v>
-      </c>
-      <c r="C17" s="79"/>
-      <c r="D17" s="138"/>
+      <c r="B17" s="59" t="s">
+        <v>170</v>
+      </c>
+      <c r="C17" s="65"/>
+      <c r="D17" s="91"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
@@ -2622,11 +2308,11 @@
     </row>
     <row r="18" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="50"/>
-      <c r="B18" s="66" t="s">
-        <v>199</v>
-      </c>
-      <c r="C18" s="79"/>
-      <c r="D18" s="138"/>
+      <c r="B18" s="59" t="s">
+        <v>171</v>
+      </c>
+      <c r="C18" s="65"/>
+      <c r="D18" s="91"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
@@ -2635,11 +2321,11 @@
     </row>
     <row r="19" spans="1:9" s="11" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A19" s="50"/>
-      <c r="B19" s="68" t="s">
+      <c r="B19" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="79"/>
-      <c r="D19" s="138"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="91"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
@@ -2648,11 +2334,11 @@
     </row>
     <row r="20" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="50"/>
-      <c r="B20" s="66" t="s">
+      <c r="B20" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="79"/>
-      <c r="D20" s="138"/>
+      <c r="C20" s="65"/>
+      <c r="D20" s="91"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
@@ -2661,11 +2347,11 @@
     </row>
     <row r="21" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="50"/>
-      <c r="B21" s="66" t="s">
+      <c r="B21" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="79"/>
-      <c r="D21" s="138"/>
+      <c r="C21" s="65"/>
+      <c r="D21" s="91"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
@@ -2673,59 +2359,59 @@
       <c r="I21" s="10"/>
     </row>
     <row r="22" spans="1:9" s="13" customFormat="1" ht="91" x14ac:dyDescent="0.3">
-      <c r="A22" s="89" t="s">
+      <c r="A22" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="61"/>
-      <c r="C22" s="80" t="s">
+      <c r="B22" s="127"/>
+      <c r="C22" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="139"/>
-      <c r="E22" s="139"/>
-      <c r="F22" s="139"/>
-      <c r="G22" s="139"/>
-      <c r="H22" s="139"/>
-      <c r="I22" s="139"/>
+      <c r="D22" s="92"/>
+      <c r="E22" s="92"/>
+      <c r="F22" s="92"/>
+      <c r="G22" s="92"/>
+      <c r="H22" s="92"/>
+      <c r="I22" s="92"/>
     </row>
     <row r="23" spans="1:9" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="51"/>
-      <c r="B23" s="94" t="s">
+      <c r="B23" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="81" t="s">
+      <c r="C23" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="D23" s="146"/>
-      <c r="E23" s="98"/>
-      <c r="F23" s="98"/>
-      <c r="G23" s="98"/>
+      <c r="D23" s="99"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="83"/>
       <c r="H23" s="14"/>
       <c r="I23" s="15"/>
     </row>
     <row r="24" spans="1:9" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="51"/>
-      <c r="B24" s="94" t="s">
+      <c r="B24" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="81" t="s">
+      <c r="C24" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="142"/>
+      <c r="D24" s="95"/>
       <c r="E24" s="17"/>
-      <c r="F24" s="99"/>
+      <c r="F24" s="84"/>
       <c r="G24" s="17"/>
       <c r="H24" s="17"/>
       <c r="I24" s="15"/>
     </row>
     <row r="25" spans="1:9" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="51"/>
-      <c r="B25" s="94" t="s">
+      <c r="B25" s="80" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="81" t="s">
+      <c r="C25" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="143"/>
+      <c r="D25" s="96"/>
       <c r="E25" s="18"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
@@ -2734,13 +2420,13 @@
     </row>
     <row r="26" spans="1:9" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="51"/>
-      <c r="B26" s="94" t="s">
+      <c r="B26" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="81" t="s">
+      <c r="C26" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="143"/>
+      <c r="D26" s="96"/>
       <c r="E26" s="18"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
@@ -2749,13 +2435,13 @@
     </row>
     <row r="27" spans="1:9" s="16" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A27" s="51"/>
-      <c r="B27" s="94" t="s">
+      <c r="B27" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="81" t="s">
+      <c r="C27" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="143"/>
+      <c r="D27" s="96"/>
       <c r="E27" s="18"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
@@ -2764,13 +2450,13 @@
     </row>
     <row r="28" spans="1:9" s="16" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A28" s="51"/>
-      <c r="B28" s="94" t="s">
+      <c r="B28" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="81" t="s">
+      <c r="C28" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="143"/>
+      <c r="D28" s="96"/>
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
@@ -2779,13 +2465,13 @@
     </row>
     <row r="29" spans="1:9" s="16" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A29" s="51"/>
-      <c r="B29" s="94" t="s">
+      <c r="B29" s="80" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="81" t="s">
+      <c r="C29" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="D29" s="143"/>
+      <c r="D29" s="96"/>
       <c r="E29" s="18"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
@@ -2794,13 +2480,13 @@
     </row>
     <row r="30" spans="1:9" s="16" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A30" s="51"/>
-      <c r="B30" s="94" t="s">
+      <c r="B30" s="80" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="81" t="s">
+      <c r="C30" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="D30" s="141"/>
+      <c r="D30" s="94"/>
       <c r="E30" s="14"/>
       <c r="F30" s="14"/>
       <c r="G30" s="14"/>
@@ -2809,13 +2495,13 @@
     </row>
     <row r="31" spans="1:9" s="16" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A31" s="51"/>
-      <c r="B31" s="94" t="s">
+      <c r="B31" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="81" t="s">
+      <c r="C31" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="D31" s="143"/>
+      <c r="D31" s="96"/>
       <c r="E31" s="18"/>
       <c r="F31" s="19"/>
       <c r="G31" s="19"/>
@@ -2824,13 +2510,13 @@
     </row>
     <row r="32" spans="1:9" s="16" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A32" s="51"/>
-      <c r="B32" s="69" t="s">
+      <c r="B32" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="81" t="s">
+      <c r="C32" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="D32" s="144"/>
+      <c r="D32" s="97"/>
       <c r="E32" s="19"/>
       <c r="F32" s="19"/>
       <c r="G32" s="19"/>
@@ -2839,13 +2525,13 @@
     </row>
     <row r="33" spans="1:9" s="16" customFormat="1" ht="65" x14ac:dyDescent="0.3">
       <c r="A33" s="51"/>
-      <c r="B33" s="69" t="s">
+      <c r="B33" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="81" t="s">
+      <c r="C33" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="D33" s="145"/>
+      <c r="D33" s="98"/>
       <c r="E33" s="20"/>
       <c r="F33" s="20"/>
       <c r="G33" s="20"/>
@@ -2854,28 +2540,28 @@
     </row>
     <row r="34" spans="1:9" s="16" customFormat="1" ht="91" x14ac:dyDescent="0.3">
       <c r="A34" s="51"/>
-      <c r="B34" s="69" t="s">
+      <c r="B34" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="81" t="s">
+      <c r="C34" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="D34" s="147"/>
+      <c r="D34" s="100"/>
       <c r="E34" s="21"/>
-      <c r="F34" s="100"/>
+      <c r="F34" s="85"/>
       <c r="G34" s="21"/>
       <c r="H34" s="21"/>
       <c r="I34" s="15"/>
     </row>
     <row r="35" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="52"/>
-      <c r="B35" s="69" t="s">
+      <c r="B35" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="C35" s="81" t="s">
+      <c r="C35" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="D35" s="143"/>
+      <c r="D35" s="96"/>
       <c r="E35" s="18"/>
       <c r="F35" s="18"/>
       <c r="G35" s="18"/>
@@ -2884,13 +2570,13 @@
     </row>
     <row r="36" spans="1:9" s="16" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A36" s="51"/>
-      <c r="B36" s="69" t="s">
+      <c r="B36" s="60" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="81" t="s">
+      <c r="C36" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="144"/>
+      <c r="D36" s="97"/>
       <c r="E36" s="19"/>
       <c r="F36" s="19"/>
       <c r="G36" s="19"/>
@@ -2899,13 +2585,13 @@
     </row>
     <row r="37" spans="1:9" s="16" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A37" s="51"/>
-      <c r="B37" s="69" t="s">
+      <c r="B37" s="60" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="81" t="s">
+      <c r="C37" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="D37" s="144"/>
+      <c r="D37" s="97"/>
       <c r="E37" s="19"/>
       <c r="F37" s="19"/>
       <c r="G37" s="19"/>
@@ -2913,11 +2599,11 @@
       <c r="I37" s="15"/>
     </row>
     <row r="38" spans="1:9" s="25" customFormat="1" ht="91" x14ac:dyDescent="0.3">
-      <c r="A38" s="90" t="s">
+      <c r="A38" s="76" t="s">
         <v>76</v>
       </c>
-      <c r="B38" s="62"/>
-      <c r="C38" s="82" t="s">
+      <c r="B38" s="128"/>
+      <c r="C38" s="68" t="s">
         <v>77</v>
       </c>
       <c r="D38" s="24"/>
@@ -2929,14 +2615,14 @@
     </row>
     <row r="39" spans="1:9" s="28" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A39" s="53"/>
-      <c r="B39" s="70" t="s">
-        <v>200</v>
-      </c>
-      <c r="C39" s="83" t="s">
-        <v>201</v>
-      </c>
-      <c r="D39" s="149" t="s">
-        <v>209</v>
+      <c r="B39" s="77" t="s">
+        <v>172</v>
+      </c>
+      <c r="C39" s="69" t="s">
+        <v>173</v>
+      </c>
+      <c r="D39" s="102" t="s">
+        <v>181</v>
       </c>
       <c r="E39" s="26"/>
       <c r="F39" s="26"/>
@@ -2946,12 +2632,12 @@
     </row>
     <row r="40" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="53"/>
-      <c r="B40" s="70" t="s">
-        <v>202</v>
-      </c>
-      <c r="C40" s="83"/>
-      <c r="D40" s="149" t="s">
-        <v>210</v>
+      <c r="B40" s="77" t="s">
+        <v>174</v>
+      </c>
+      <c r="C40" s="69"/>
+      <c r="D40" s="102" t="s">
+        <v>182</v>
       </c>
       <c r="E40" s="26"/>
       <c r="F40" s="26"/>
@@ -2961,25 +2647,25 @@
     </row>
     <row r="41" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="53"/>
-      <c r="B41" s="70" t="s">
-        <v>203</v>
-      </c>
-      <c r="C41" s="83"/>
-      <c r="D41" s="149"/>
+      <c r="B41" s="77" t="s">
+        <v>175</v>
+      </c>
+      <c r="C41" s="69"/>
+      <c r="D41" s="102"/>
       <c r="E41" s="26"/>
       <c r="F41" s="26"/>
       <c r="G41" s="26"/>
       <c r="H41" s="26"/>
       <c r="I41" s="27"/>
     </row>
-    <row r="42" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" s="28" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A42" s="53"/>
-      <c r="B42" s="70" t="s">
-        <v>204</v>
-      </c>
-      <c r="C42" s="83"/>
-      <c r="D42" s="149" t="s">
-        <v>211</v>
+      <c r="B42" s="77" t="s">
+        <v>176</v>
+      </c>
+      <c r="C42" s="69"/>
+      <c r="D42" s="102" t="s">
+        <v>183</v>
       </c>
       <c r="E42" s="26"/>
       <c r="F42" s="26"/>
@@ -2989,11 +2675,11 @@
     </row>
     <row r="43" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="53"/>
-      <c r="B43" s="70" t="s">
-        <v>205</v>
-      </c>
-      <c r="C43" s="83"/>
-      <c r="D43" s="149">
+      <c r="B43" s="77" t="s">
+        <v>177</v>
+      </c>
+      <c r="C43" s="69"/>
+      <c r="D43" s="102">
         <v>90909</v>
       </c>
       <c r="E43" s="26"/>
@@ -3004,12 +2690,12 @@
     </row>
     <row r="44" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="53"/>
-      <c r="B44" s="70" t="s">
-        <v>206</v>
-      </c>
-      <c r="C44" s="83"/>
-      <c r="D44" s="155" t="s">
-        <v>232</v>
+      <c r="B44" s="77" t="s">
+        <v>178</v>
+      </c>
+      <c r="C44" s="69"/>
+      <c r="D44" s="108" t="s">
+        <v>204</v>
       </c>
       <c r="E44" s="26"/>
       <c r="F44" s="26"/>
@@ -3019,116 +2705,116 @@
     </row>
     <row r="45" spans="1:9" s="28" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A45" s="53"/>
-      <c r="B45" s="71" t="s">
-        <v>212</v>
-      </c>
-      <c r="C45" s="83" t="s">
-        <v>213</v>
-      </c>
-      <c r="D45" s="149" t="s">
-        <v>219</v>
-      </c>
-      <c r="E45" s="156"/>
+      <c r="B45" s="129" t="s">
+        <v>184</v>
+      </c>
+      <c r="C45" s="69" t="s">
+        <v>185</v>
+      </c>
+      <c r="D45" s="102" t="s">
+        <v>191</v>
+      </c>
+      <c r="E45" s="109"/>
       <c r="F45" s="26"/>
-      <c r="G45" s="156"/>
-      <c r="H45" s="156"/>
+      <c r="G45" s="109"/>
+      <c r="H45" s="109"/>
       <c r="I45" s="27"/>
     </row>
     <row r="46" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="53"/>
-      <c r="B46" s="71" t="s">
-        <v>214</v>
-      </c>
-      <c r="C46" s="83"/>
-      <c r="D46" s="149" t="s">
-        <v>220</v>
-      </c>
-      <c r="E46" s="156"/>
+      <c r="B46" s="129" t="s">
+        <v>186</v>
+      </c>
+      <c r="C46" s="69"/>
+      <c r="D46" s="102" t="s">
+        <v>192</v>
+      </c>
+      <c r="E46" s="109"/>
       <c r="F46" s="26"/>
-      <c r="G46" s="156"/>
-      <c r="H46" s="156"/>
+      <c r="G46" s="109"/>
+      <c r="H46" s="109"/>
       <c r="I46" s="27"/>
     </row>
     <row r="47" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="53"/>
-      <c r="B47" s="71" t="s">
-        <v>215</v>
-      </c>
-      <c r="C47" s="83"/>
-      <c r="D47" s="149"/>
-      <c r="E47" s="156"/>
+      <c r="B47" s="129" t="s">
+        <v>187</v>
+      </c>
+      <c r="C47" s="69"/>
+      <c r="D47" s="102"/>
+      <c r="E47" s="109"/>
       <c r="F47" s="26"/>
-      <c r="G47" s="156"/>
-      <c r="H47" s="156"/>
+      <c r="G47" s="109"/>
+      <c r="H47" s="109"/>
       <c r="I47" s="27"/>
     </row>
-    <row r="48" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" s="28" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A48" s="53"/>
-      <c r="B48" s="71" t="s">
-        <v>216</v>
-      </c>
-      <c r="C48" s="83"/>
-      <c r="D48" s="149" t="s">
-        <v>211</v>
-      </c>
-      <c r="E48" s="156"/>
+      <c r="B48" s="129" t="s">
+        <v>188</v>
+      </c>
+      <c r="C48" s="69"/>
+      <c r="D48" s="102" t="s">
+        <v>183</v>
+      </c>
+      <c r="E48" s="109"/>
       <c r="F48" s="26"/>
-      <c r="G48" s="156"/>
-      <c r="H48" s="156"/>
+      <c r="G48" s="109"/>
+      <c r="H48" s="109"/>
       <c r="I48" s="27"/>
     </row>
     <row r="49" spans="1:47" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="53"/>
-      <c r="B49" s="71" t="s">
-        <v>217</v>
-      </c>
-      <c r="C49" s="83"/>
-      <c r="D49" s="149">
+      <c r="B49" s="129" t="s">
+        <v>189</v>
+      </c>
+      <c r="C49" s="69"/>
+      <c r="D49" s="102">
         <v>30445</v>
       </c>
-      <c r="E49" s="156"/>
+      <c r="E49" s="109"/>
       <c r="F49" s="26"/>
-      <c r="G49" s="156"/>
-      <c r="H49" s="156"/>
+      <c r="G49" s="109"/>
+      <c r="H49" s="109"/>
       <c r="I49" s="27"/>
     </row>
     <row r="50" spans="1:47" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="53"/>
-      <c r="B50" s="71" t="s">
-        <v>218</v>
-      </c>
-      <c r="C50" s="83"/>
-      <c r="D50" s="149"/>
-      <c r="E50" s="156"/>
+      <c r="B50" s="129" t="s">
+        <v>190</v>
+      </c>
+      <c r="C50" s="69"/>
+      <c r="D50" s="102"/>
+      <c r="E50" s="109"/>
       <c r="F50" s="26"/>
-      <c r="G50" s="156"/>
-      <c r="H50" s="156"/>
+      <c r="G50" s="109"/>
+      <c r="H50" s="109"/>
       <c r="I50" s="27"/>
     </row>
     <row r="51" spans="1:47" s="28" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A51" s="53"/>
-      <c r="B51" s="70" t="s">
+      <c r="B51" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="C51" s="83" t="s">
+      <c r="C51" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="D51" s="149"/>
-      <c r="E51" s="149"/>
-      <c r="F51" s="149"/>
-      <c r="G51" s="149"/>
-      <c r="H51" s="149"/>
+      <c r="D51" s="102"/>
+      <c r="E51" s="102"/>
+      <c r="F51" s="102"/>
+      <c r="G51" s="102"/>
+      <c r="H51" s="102"/>
       <c r="I51" s="27"/>
     </row>
     <row r="52" spans="1:47" s="28" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A52" s="53"/>
-      <c r="B52" s="91" t="s">
+      <c r="B52" s="77" t="s">
         <v>81</v>
       </c>
-      <c r="C52" s="83" t="s">
+      <c r="C52" s="69" t="s">
         <v>82</v>
       </c>
-      <c r="D52" s="149"/>
+      <c r="D52" s="102"/>
       <c r="E52" s="26"/>
       <c r="F52" s="26"/>
       <c r="G52" s="26"/>
@@ -3136,14 +2822,14 @@
       <c r="I52" s="27"/>
     </row>
     <row r="53" spans="1:47" s="31" customFormat="1" ht="65" x14ac:dyDescent="0.3">
-      <c r="A53" s="97" t="s">
+      <c r="A53" s="82" t="s">
         <v>83</v>
       </c>
-      <c r="B53" s="63"/>
-      <c r="C53" s="84" t="s">
+      <c r="B53" s="130"/>
+      <c r="C53" s="70" t="s">
         <v>84</v>
       </c>
-      <c r="D53" s="150"/>
+      <c r="D53" s="103"/>
       <c r="E53" s="29"/>
       <c r="F53" s="29"/>
       <c r="G53" s="29"/>
@@ -3152,14 +2838,14 @@
     </row>
     <row r="54" spans="1:47" s="34" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A54" s="54"/>
-      <c r="B54" s="72" t="s">
+      <c r="B54" s="131" t="s">
         <v>85</v>
       </c>
-      <c r="C54" s="85" t="s">
+      <c r="C54" s="71" t="s">
         <v>86</v>
       </c>
       <c r="D54" s="32" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="E54" s="32"/>
       <c r="F54" s="32"/>
@@ -3169,14 +2855,14 @@
     </row>
     <row r="55" spans="1:47" s="34" customFormat="1" ht="91" x14ac:dyDescent="0.3">
       <c r="A55" s="54"/>
-      <c r="B55" s="72" t="s">
+      <c r="B55" s="131" t="s">
         <v>87</v>
       </c>
-      <c r="C55" s="85" t="s">
+      <c r="C55" s="71" t="s">
         <v>88</v>
       </c>
       <c r="D55" s="35" t="s">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="E55" s="35"/>
       <c r="F55" s="35"/>
@@ -3186,25 +2872,25 @@
     </row>
     <row r="56" spans="1:47" s="34" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A56" s="54"/>
-      <c r="B56" s="72" t="s">
+      <c r="B56" s="131" t="s">
         <v>89</v>
       </c>
-      <c r="C56" s="85" t="s">
+      <c r="C56" s="71" t="s">
         <v>90</v>
       </c>
-      <c r="D56" s="148"/>
-      <c r="E56" s="148"/>
-      <c r="F56" s="148"/>
-      <c r="G56" s="148"/>
-      <c r="H56" s="148"/>
+      <c r="D56" s="101"/>
+      <c r="E56" s="101"/>
+      <c r="F56" s="101"/>
+      <c r="G56" s="101"/>
+      <c r="H56" s="101"/>
       <c r="I56" s="33"/>
     </row>
     <row r="57" spans="1:47" s="34" customFormat="1" ht="65" x14ac:dyDescent="0.3">
       <c r="A57" s="54"/>
-      <c r="B57" s="72" t="s">
+      <c r="B57" s="131" t="s">
         <v>92</v>
       </c>
-      <c r="C57" s="85" t="s">
+      <c r="C57" s="71" t="s">
         <v>93</v>
       </c>
       <c r="D57" s="36"/>
@@ -3216,10 +2902,10 @@
     </row>
     <row r="58" spans="1:47" s="34" customFormat="1" ht="91" x14ac:dyDescent="0.3">
       <c r="A58" s="54"/>
-      <c r="B58" s="72" t="s">
+      <c r="B58" s="131" t="s">
         <v>94</v>
       </c>
-      <c r="C58" s="85" t="s">
+      <c r="C58" s="71" t="s">
         <v>95</v>
       </c>
       <c r="D58" s="35"/>
@@ -3231,27 +2917,27 @@
     </row>
     <row r="59" spans="1:47" s="34" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A59" s="54"/>
-      <c r="B59" s="72" t="s">
+      <c r="B59" s="131" t="s">
         <v>96</v>
       </c>
-      <c r="C59" s="85" t="s">
+      <c r="C59" s="71" t="s">
         <v>97</v>
       </c>
-      <c r="D59" s="148" t="s">
+      <c r="D59" s="101" t="s">
         <v>140</v>
       </c>
-      <c r="E59" s="148"/>
-      <c r="F59" s="148"/>
-      <c r="G59" s="148"/>
-      <c r="H59" s="148"/>
+      <c r="E59" s="101"/>
+      <c r="F59" s="101"/>
+      <c r="G59" s="101"/>
+      <c r="H59" s="101"/>
       <c r="I59" s="33"/>
     </row>
     <row r="60" spans="1:47" s="38" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A60" s="55" t="s">
         <v>99</v>
       </c>
-      <c r="B60" s="64"/>
-      <c r="C60" s="86" t="s">
+      <c r="B60" s="132"/>
+      <c r="C60" s="72" t="s">
         <v>100</v>
       </c>
       <c r="D60" s="37"/>
@@ -3263,13 +2949,13 @@
     </row>
     <row r="61" spans="1:47" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="56"/>
-      <c r="B61" s="73" t="s">
+      <c r="B61" s="133" t="s">
         <v>101</v>
       </c>
-      <c r="C61" s="87" t="s">
+      <c r="C61" s="73" t="s">
         <v>102</v>
       </c>
-      <c r="D61" s="151"/>
+      <c r="D61" s="104"/>
       <c r="E61" s="39"/>
       <c r="F61" s="39"/>
       <c r="G61" s="39"/>
@@ -3278,13 +2964,13 @@
     </row>
     <row r="62" spans="1:47" s="41" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A62" s="56"/>
-      <c r="B62" s="73" t="s">
+      <c r="B62" s="133" t="s">
         <v>103</v>
       </c>
-      <c r="C62" s="87" t="s">
+      <c r="C62" s="73" t="s">
         <v>104</v>
       </c>
-      <c r="D62" s="151"/>
+      <c r="D62" s="104"/>
       <c r="E62" s="39"/>
       <c r="F62" s="39"/>
       <c r="G62" s="39"/>
@@ -3293,32 +2979,32 @@
     </row>
     <row r="63" spans="1:47" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="56"/>
-      <c r="B63" s="73" t="s">
+      <c r="B63" s="133" t="s">
         <v>105</v>
       </c>
-      <c r="C63" s="87" t="s">
+      <c r="C63" s="73" t="s">
         <v>106</v>
       </c>
-      <c r="D63" s="151"/>
-      <c r="E63" s="151"/>
-      <c r="F63" s="151"/>
-      <c r="G63" s="151"/>
-      <c r="H63" s="151"/>
+      <c r="D63" s="104"/>
+      <c r="E63" s="104"/>
+      <c r="F63" s="104"/>
+      <c r="G63" s="104"/>
+      <c r="H63" s="104"/>
       <c r="I63" s="56"/>
     </row>
     <row r="64" spans="1:47" s="42" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A64" s="56"/>
-      <c r="B64" s="73" t="s">
+      <c r="B64" s="133" t="s">
         <v>107</v>
       </c>
-      <c r="C64" s="87" t="s">
+      <c r="C64" s="73" t="s">
         <v>108</v>
       </c>
-      <c r="D64" s="151"/>
-      <c r="E64" s="151"/>
-      <c r="F64" s="151"/>
-      <c r="G64" s="151"/>
-      <c r="H64" s="151"/>
+      <c r="D64" s="104"/>
+      <c r="E64" s="104"/>
+      <c r="F64" s="104"/>
+      <c r="G64" s="104"/>
+      <c r="H64" s="104"/>
       <c r="I64" s="56"/>
       <c r="J64" s="56"/>
       <c r="K64" s="56"/>
@@ -3361,15 +3047,15 @@
     </row>
     <row r="65" spans="1:47" s="45" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="56"/>
-      <c r="B65" s="73" t="s">
+      <c r="B65" s="133" t="s">
         <v>109</v>
       </c>
-      <c r="C65" s="87"/>
-      <c r="D65" s="151"/>
-      <c r="E65" s="151"/>
-      <c r="F65" s="151"/>
-      <c r="G65" s="151"/>
-      <c r="H65" s="151"/>
+      <c r="C65" s="73"/>
+      <c r="D65" s="104"/>
+      <c r="E65" s="104"/>
+      <c r="F65" s="104"/>
+      <c r="G65" s="104"/>
+      <c r="H65" s="104"/>
       <c r="I65" s="56"/>
       <c r="J65" s="56"/>
       <c r="K65" s="56"/>
@@ -3410,17 +3096,17 @@
       <c r="AT65" s="56"/>
       <c r="AU65" s="56"/>
     </row>
-    <row r="66" spans="1:47" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:47" s="45" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A66" s="56"/>
-      <c r="B66" s="73" t="s">
+      <c r="B66" s="133" t="s">
         <v>110</v>
       </c>
-      <c r="C66" s="87"/>
-      <c r="D66" s="151"/>
-      <c r="E66" s="151"/>
-      <c r="F66" s="151"/>
-      <c r="G66" s="151"/>
-      <c r="H66" s="151"/>
+      <c r="C66" s="73"/>
+      <c r="D66" s="104"/>
+      <c r="E66" s="104"/>
+      <c r="F66" s="104"/>
+      <c r="G66" s="104"/>
+      <c r="H66" s="104"/>
       <c r="I66" s="56"/>
       <c r="J66" s="56"/>
       <c r="K66" s="56"/>
@@ -3461,17 +3147,17 @@
       <c r="AT66" s="56"/>
       <c r="AU66" s="56"/>
     </row>
-    <row r="67" spans="1:47" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:47" s="45" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A67" s="56"/>
-      <c r="B67" s="73" t="s">
+      <c r="B67" s="133" t="s">
         <v>111</v>
       </c>
-      <c r="C67" s="87"/>
-      <c r="D67" s="151"/>
-      <c r="E67" s="151"/>
-      <c r="F67" s="151"/>
-      <c r="G67" s="151"/>
-      <c r="H67" s="151"/>
+      <c r="C67" s="73"/>
+      <c r="D67" s="104"/>
+      <c r="E67" s="104"/>
+      <c r="F67" s="104"/>
+      <c r="G67" s="104"/>
+      <c r="H67" s="104"/>
       <c r="I67" s="56"/>
       <c r="J67" s="56"/>
       <c r="K67" s="56"/>
@@ -3512,17 +3198,17 @@
       <c r="AT67" s="56"/>
       <c r="AU67" s="56"/>
     </row>
-    <row r="68" spans="1:47" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:47" s="45" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A68" s="56"/>
-      <c r="B68" s="73" t="s">
+      <c r="B68" s="133" t="s">
         <v>112</v>
       </c>
-      <c r="C68" s="87"/>
-      <c r="D68" s="151"/>
-      <c r="E68" s="151"/>
-      <c r="F68" s="151"/>
-      <c r="G68" s="151"/>
-      <c r="H68" s="151"/>
+      <c r="C68" s="73"/>
+      <c r="D68" s="104"/>
+      <c r="E68" s="104"/>
+      <c r="F68" s="104"/>
+      <c r="G68" s="104"/>
+      <c r="H68" s="104"/>
       <c r="I68" s="56"/>
       <c r="J68" s="56"/>
       <c r="K68" s="56"/>
@@ -3563,41 +3249,41 @@
       <c r="AT68" s="56"/>
       <c r="AU68" s="56"/>
     </row>
-    <row r="69" spans="1:47" s="105" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="101" t="s">
+    <row r="69" spans="1:47" s="89" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="86" t="s">
         <v>163</v>
       </c>
-      <c r="B69" s="102"/>
-      <c r="C69" s="103"/>
-      <c r="D69" s="104"/>
-      <c r="E69" s="104"/>
-      <c r="F69" s="104"/>
-      <c r="G69" s="104"/>
-      <c r="H69" s="104"/>
-      <c r="I69" s="104"/>
+      <c r="B69" s="134"/>
+      <c r="C69" s="87"/>
+      <c r="D69" s="88"/>
+      <c r="E69" s="88"/>
+      <c r="F69" s="88"/>
+      <c r="G69" s="88"/>
+      <c r="H69" s="88"/>
+      <c r="I69" s="88"/>
     </row>
     <row r="70" spans="1:47" s="45" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A70" s="57"/>
-      <c r="B70" s="74" t="s">
+      <c r="B70" s="61" t="s">
         <v>113</v>
       </c>
-      <c r="C70" s="88" t="s">
+      <c r="C70" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="D70" s="152"/>
-      <c r="E70" s="152"/>
-      <c r="F70" s="152"/>
-      <c r="G70" s="152"/>
+      <c r="D70" s="105"/>
+      <c r="E70" s="105"/>
+      <c r="F70" s="105"/>
+      <c r="G70" s="105"/>
       <c r="H70" s="43"/>
       <c r="I70" s="44"/>
     </row>
     <row r="71" spans="1:47" s="45" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="57"/>
-      <c r="B71" s="74" t="s">
+      <c r="B71" s="61" t="s">
         <v>115</v>
       </c>
-      <c r="C71" s="88"/>
-      <c r="D71" s="152"/>
+      <c r="C71" s="74"/>
+      <c r="D71" s="105"/>
       <c r="E71" s="43"/>
       <c r="F71" s="43"/>
       <c r="G71" s="43"/>
@@ -3606,11 +3292,11 @@
     </row>
     <row r="72" spans="1:47" s="45" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="57"/>
-      <c r="B72" s="74" t="s">
+      <c r="B72" s="61" t="s">
         <v>116</v>
       </c>
-      <c r="C72" s="88"/>
-      <c r="D72" s="152"/>
+      <c r="C72" s="74"/>
+      <c r="D72" s="105"/>
       <c r="E72" s="43"/>
       <c r="F72" s="43"/>
       <c r="G72" s="43"/>
@@ -3619,11 +3305,11 @@
     </row>
     <row r="73" spans="1:47" s="45" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A73" s="57"/>
-      <c r="B73" s="75" t="s">
+      <c r="B73" s="61" t="s">
         <v>117</v>
       </c>
-      <c r="C73" s="88"/>
-      <c r="D73" s="152"/>
+      <c r="C73" s="74"/>
+      <c r="D73" s="105"/>
       <c r="E73" s="43"/>
       <c r="F73" s="43"/>
       <c r="G73" s="43"/>
@@ -3632,11 +3318,11 @@
     </row>
     <row r="74" spans="1:47" s="45" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A74" s="57"/>
-      <c r="B74" s="75" t="s">
+      <c r="B74" s="61" t="s">
         <v>118</v>
       </c>
-      <c r="C74" s="88"/>
-      <c r="D74" s="152"/>
+      <c r="C74" s="74"/>
+      <c r="D74" s="105"/>
       <c r="E74" s="43"/>
       <c r="F74" s="43"/>
       <c r="G74" s="43"/>
@@ -3645,14 +3331,14 @@
     </row>
     <row r="75" spans="1:47" s="45" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A75" s="57"/>
-      <c r="B75" s="74" t="s">
+      <c r="B75" s="61" t="s">
         <v>119</v>
       </c>
-      <c r="C75" s="88" t="s">
+      <c r="C75" s="74" t="s">
         <v>120</v>
       </c>
-      <c r="D75" s="152" t="s">
-        <v>233</v>
+      <c r="D75" s="105" t="s">
+        <v>205</v>
       </c>
       <c r="E75" s="43"/>
       <c r="F75" s="43"/>
@@ -3662,14 +3348,14 @@
     </row>
     <row r="76" spans="1:47" s="45" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A76" s="57"/>
-      <c r="B76" s="74" t="s">
-        <v>225</v>
-      </c>
-      <c r="C76" s="88" t="s">
-        <v>226</v>
-      </c>
-      <c r="D76" s="152" t="s">
-        <v>231</v>
+      <c r="B76" s="61" t="s">
+        <v>197</v>
+      </c>
+      <c r="C76" s="74" t="s">
+        <v>198</v>
+      </c>
+      <c r="D76" s="105" t="s">
+        <v>203</v>
       </c>
       <c r="E76" s="43"/>
       <c r="F76" s="43"/>
@@ -3679,13 +3365,13 @@
     </row>
     <row r="77" spans="1:47" s="45" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A77" s="57"/>
-      <c r="B77" s="74" t="s">
-        <v>227</v>
-      </c>
-      <c r="C77" s="88" t="s">
-        <v>228</v>
-      </c>
-      <c r="D77" s="152">
+      <c r="B77" s="61" t="s">
+        <v>199</v>
+      </c>
+      <c r="C77" s="74" t="s">
+        <v>200</v>
+      </c>
+      <c r="D77" s="105">
         <v>7890123456</v>
       </c>
       <c r="E77" s="43"/>
@@ -3696,13 +3382,13 @@
     </row>
     <row r="78" spans="1:47" s="45" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="57"/>
-      <c r="B78" s="74" t="s">
-        <v>229</v>
-      </c>
-      <c r="C78" s="88" t="s">
-        <v>230</v>
-      </c>
-      <c r="D78" s="157">
+      <c r="B78" s="61" t="s">
+        <v>201</v>
+      </c>
+      <c r="C78" s="74" t="s">
+        <v>202</v>
+      </c>
+      <c r="D78" s="110">
         <v>45340</v>
       </c>
       <c r="E78" s="43"/>
@@ -3713,14 +3399,14 @@
     </row>
     <row r="79" spans="1:47" s="45" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" s="57"/>
-      <c r="B79" s="74" t="s">
+      <c r="B79" s="61" t="s">
         <v>121</v>
       </c>
-      <c r="C79" s="88" t="s">
+      <c r="C79" s="74" t="s">
         <v>122</v>
       </c>
-      <c r="D79" s="152" t="s">
-        <v>222</v>
+      <c r="D79" s="105" t="s">
+        <v>194</v>
       </c>
       <c r="E79" s="43"/>
       <c r="F79" s="43"/>
@@ -3728,174 +3414,208 @@
       <c r="H79" s="43"/>
       <c r="I79" s="44"/>
     </row>
-    <row r="80" spans="1:47" s="162" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="158" t="s">
+    <row r="80" spans="1:47" s="114" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="111" t="s">
+        <v>206</v>
+      </c>
+      <c r="B80" s="135"/>
+      <c r="C80" s="112"/>
+      <c r="D80" s="113"/>
+      <c r="E80" s="113"/>
+      <c r="F80" s="113"/>
+      <c r="G80" s="113"/>
+      <c r="H80" s="113"/>
+      <c r="I80" s="113"/>
+    </row>
+    <row r="81" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="115"/>
+      <c r="B81" s="120" t="s">
+        <v>207</v>
+      </c>
+      <c r="C81" s="116" t="s">
+        <v>208</v>
+      </c>
+      <c r="D81" s="117" t="s">
+        <v>214</v>
+      </c>
+      <c r="E81" s="117"/>
+      <c r="F81" s="117"/>
+      <c r="G81" s="117"/>
+      <c r="H81" s="117"/>
+      <c r="I81" s="118"/>
+    </row>
+    <row r="82" spans="1:9" s="119" customFormat="1" ht="26" x14ac:dyDescent="0.3">
+      <c r="A82" s="115"/>
+      <c r="B82" s="120" t="s">
+        <v>224</v>
+      </c>
+      <c r="C82" s="116" t="s">
+        <v>225</v>
+      </c>
+      <c r="D82" s="117" t="s">
+        <v>226</v>
+      </c>
+      <c r="E82" s="117"/>
+      <c r="F82" s="117"/>
+      <c r="G82" s="117"/>
+      <c r="H82" s="117"/>
+      <c r="I82" s="118"/>
+    </row>
+    <row r="83" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="115"/>
+      <c r="B83" s="120" t="s">
+        <v>231</v>
+      </c>
+      <c r="C83" s="116" t="s">
+        <v>232</v>
+      </c>
+      <c r="D83" s="117" t="s">
+        <v>235</v>
+      </c>
+      <c r="E83" s="117"/>
+      <c r="F83" s="117"/>
+      <c r="G83" s="117"/>
+      <c r="H83" s="117"/>
+      <c r="I83" s="118"/>
+    </row>
+    <row r="84" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="115"/>
+      <c r="B84" s="137" t="s">
+        <v>233</v>
+      </c>
+      <c r="C84" s="119" t="s">
         <v>234</v>
       </c>
-      <c r="B80" s="159"/>
-      <c r="C80" s="160"/>
-      <c r="D80" s="161"/>
-      <c r="E80" s="161"/>
-      <c r="F80" s="161"/>
-      <c r="G80" s="161"/>
-      <c r="H80" s="161"/>
-      <c r="I80" s="161"/>
-    </row>
-    <row r="81" spans="1:9" s="168" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="163"/>
-      <c r="B81" s="164" t="s">
-        <v>235</v>
-      </c>
-      <c r="C81" s="165" t="s">
-        <v>236</v>
-      </c>
-      <c r="D81" s="166" t="s">
-        <v>242</v>
-      </c>
-      <c r="E81" s="166"/>
-      <c r="F81" s="166"/>
-      <c r="G81" s="166"/>
-      <c r="H81" s="166"/>
-      <c r="I81" s="167"/>
-    </row>
-    <row r="82" spans="1:9" s="168" customFormat="1" ht="26" x14ac:dyDescent="0.3">
-      <c r="A82" s="163"/>
-      <c r="B82" s="164" t="s">
-        <v>252</v>
-      </c>
-      <c r="C82" s="165" t="s">
-        <v>253</v>
-      </c>
-      <c r="D82" s="166" t="s">
-        <v>254</v>
-      </c>
-      <c r="E82" s="166"/>
-      <c r="F82" s="166"/>
-      <c r="G82" s="166"/>
-      <c r="H82" s="166"/>
-      <c r="I82" s="167"/>
-    </row>
-    <row r="83" spans="1:9" s="168" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="163"/>
-      <c r="B83" s="164" t="s">
-        <v>245</v>
-      </c>
-      <c r="C83" s="165"/>
-      <c r="D83" s="166" t="s">
-        <v>247</v>
-      </c>
-      <c r="E83" s="166"/>
-      <c r="F83" s="166"/>
-      <c r="G83" s="166"/>
-      <c r="H83" s="166"/>
-      <c r="I83" s="167"/>
-    </row>
-    <row r="84" spans="1:9" s="168" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="163"/>
-      <c r="B84" s="164" t="s">
-        <v>246</v>
-      </c>
-      <c r="C84" s="165"/>
-      <c r="D84" s="166" t="s">
-        <v>248</v>
-      </c>
-      <c r="E84" s="166"/>
-      <c r="F84" s="166"/>
-      <c r="G84" s="166"/>
-      <c r="H84" s="166"/>
-      <c r="I84" s="167"/>
-    </row>
-    <row r="85" spans="1:9" s="168" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="163"/>
-      <c r="B85" s="164" t="s">
-        <v>237</v>
-      </c>
-      <c r="C85" s="165"/>
-      <c r="D85" s="166" t="s">
-        <v>243</v>
-      </c>
-      <c r="E85" s="166"/>
-      <c r="F85" s="166"/>
-      <c r="G85" s="166"/>
-      <c r="H85" s="166"/>
-      <c r="I85" s="167"/>
-    </row>
-    <row r="86" spans="1:9" s="168" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="163"/>
-      <c r="B86" s="164" t="s">
-        <v>238</v>
-      </c>
-      <c r="C86" s="165"/>
-      <c r="D86" s="166" t="s">
+      <c r="D84" s="117">
+        <v>90876</v>
+      </c>
+      <c r="E84" s="117"/>
+      <c r="F84" s="117"/>
+      <c r="G84" s="117"/>
+      <c r="H84" s="117"/>
+      <c r="I84" s="118"/>
+    </row>
+    <row r="85" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="115"/>
+      <c r="B85" s="120" t="s">
+        <v>217</v>
+      </c>
+      <c r="C85" s="116"/>
+      <c r="D85" s="117" t="s">
+        <v>219</v>
+      </c>
+      <c r="E85" s="117"/>
+      <c r="F85" s="117"/>
+      <c r="G85" s="117"/>
+      <c r="H85" s="117"/>
+      <c r="I85" s="118"/>
+    </row>
+    <row r="86" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="115"/>
+      <c r="B86" s="120" t="s">
+        <v>218</v>
+      </c>
+      <c r="C86" s="116"/>
+      <c r="D86" s="117" t="s">
+        <v>220</v>
+      </c>
+      <c r="E86" s="117"/>
+      <c r="F86" s="117"/>
+      <c r="G86" s="117"/>
+      <c r="H86" s="117"/>
+      <c r="I86" s="118"/>
+    </row>
+    <row r="87" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="115"/>
+      <c r="B87" s="120" t="s">
+        <v>209</v>
+      </c>
+      <c r="C87" s="116"/>
+      <c r="D87" s="117" t="s">
+        <v>215</v>
+      </c>
+      <c r="E87" s="117"/>
+      <c r="F87" s="117"/>
+      <c r="G87" s="117"/>
+      <c r="H87" s="117"/>
+      <c r="I87" s="118"/>
+    </row>
+    <row r="88" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="115"/>
+      <c r="B88" s="120" t="s">
         <v>210</v>
       </c>
-      <c r="E86" s="166"/>
-      <c r="F86" s="166"/>
-      <c r="G86" s="166"/>
-      <c r="H86" s="166"/>
-      <c r="I86" s="167"/>
-    </row>
-    <row r="87" spans="1:9" s="168" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="163"/>
-      <c r="B87" s="164" t="s">
-        <v>239</v>
-      </c>
-      <c r="C87" s="165"/>
-      <c r="D87" s="166" t="s">
-        <v>244</v>
-      </c>
-      <c r="E87" s="166"/>
-      <c r="F87" s="166"/>
-      <c r="G87" s="166"/>
-      <c r="H87" s="166"/>
-      <c r="I87" s="167"/>
-    </row>
-    <row r="88" spans="1:9" s="168" customFormat="1" ht="31" x14ac:dyDescent="0.3">
-      <c r="A88" s="163"/>
-      <c r="B88" s="169" t="s">
-        <v>240</v>
-      </c>
-      <c r="C88" s="165"/>
-      <c r="D88" s="166" t="s">
+      <c r="C88" s="116"/>
+      <c r="D88" s="117" t="s">
+        <v>182</v>
+      </c>
+      <c r="E88" s="117"/>
+      <c r="F88" s="117"/>
+      <c r="G88" s="117"/>
+      <c r="H88" s="117"/>
+      <c r="I88" s="118"/>
+    </row>
+    <row r="89" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="115"/>
+      <c r="B89" s="120" t="s">
         <v>211</v>
       </c>
-      <c r="E88" s="166"/>
-      <c r="F88" s="166"/>
-      <c r="G88" s="166"/>
-      <c r="H88" s="166"/>
-      <c r="I88" s="167"/>
-    </row>
-    <row r="89" spans="1:9" s="168" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="163"/>
-      <c r="B89" s="164" t="s">
-        <v>241</v>
-      </c>
-      <c r="C89" s="165"/>
-      <c r="D89" s="166">
+      <c r="C89" s="116"/>
+      <c r="D89" s="117" t="s">
+        <v>216</v>
+      </c>
+      <c r="E89" s="117"/>
+      <c r="F89" s="117"/>
+      <c r="G89" s="117"/>
+      <c r="H89" s="117"/>
+      <c r="I89" s="118"/>
+    </row>
+    <row r="90" spans="1:9" s="119" customFormat="1" ht="31" x14ac:dyDescent="0.3">
+      <c r="A90" s="115"/>
+      <c r="B90" s="120" t="s">
+        <v>212</v>
+      </c>
+      <c r="C90" s="116"/>
+      <c r="D90" s="117" t="s">
+        <v>183</v>
+      </c>
+      <c r="E90" s="117"/>
+      <c r="F90" s="117"/>
+      <c r="G90" s="117"/>
+      <c r="H90" s="117"/>
+      <c r="I90" s="118"/>
+    </row>
+    <row r="91" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="115"/>
+      <c r="B91" s="120" t="s">
+        <v>213</v>
+      </c>
+      <c r="C91" s="116"/>
+      <c r="D91" s="117">
         <v>10203</v>
       </c>
-      <c r="E89" s="166"/>
-      <c r="F89" s="166"/>
-      <c r="G89" s="166"/>
-      <c r="H89" s="166"/>
-      <c r="I89" s="167"/>
-    </row>
-    <row r="90" spans="1:9" s="168" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="163"/>
-      <c r="B90" s="170" t="s">
-        <v>250</v>
-      </c>
-      <c r="C90" s="165" t="s">
-        <v>251</v>
-      </c>
-      <c r="D90" s="171" t="e" vm="1">
+      <c r="E91" s="117"/>
+      <c r="F91" s="117"/>
+      <c r="G91" s="117"/>
+      <c r="H91" s="117"/>
+      <c r="I91" s="118"/>
+    </row>
+    <row r="92" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="115"/>
+      <c r="B92" s="136" t="s">
+        <v>222</v>
+      </c>
+      <c r="C92" s="116" t="s">
+        <v>223</v>
+      </c>
+      <c r="D92" s="121" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="E90" s="166"/>
-      <c r="F90" s="166"/>
-      <c r="G90" s="166"/>
-      <c r="H90" s="166"/>
-      <c r="I90" s="167"/>
+      <c r="E92" s="117"/>
+      <c r="F92" s="117"/>
+      <c r="G92" s="117"/>
+      <c r="H92" s="117"/>
+      <c r="I92" s="118"/>
     </row>
   </sheetData>
   <sheetProtection deleteColumns="0" selectLockedCells="1"/>
@@ -3917,370 +3637,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C559A218-9020-4822-8346-393500FE199B}">
-  <dimension ref="A1:I69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="21" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="27.33203125" style="46" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="58" customWidth="1"/>
-    <col min="3" max="3" width="39.1640625" style="65" customWidth="1"/>
-    <col min="4" max="8" width="32.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.83203125" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="65" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="65" x14ac:dyDescent="0.3">
-      <c r="C2" s="65" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" s="114" customFormat="1" ht="39" x14ac:dyDescent="0.3">
-      <c r="A3" s="112" t="s">
-        <v>165</v>
-      </c>
-      <c r="B3" s="115"/>
-      <c r="C3" s="116" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="113"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="113"/>
-      <c r="G3" s="113"/>
-      <c r="H3" s="113"/>
-      <c r="I3" s="113"/>
-    </row>
-    <row r="4" spans="1:9" s="108" customFormat="1" ht="169" x14ac:dyDescent="0.3">
-      <c r="A4" s="107"/>
-      <c r="B4" s="109" t="s">
-        <v>185</v>
-      </c>
-      <c r="C4" s="110" t="s">
-        <v>186</v>
-      </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="106"/>
-    </row>
-    <row r="5" spans="1:9" s="108" customFormat="1" ht="78" x14ac:dyDescent="0.3">
-      <c r="A5" s="107"/>
-      <c r="B5" s="109" t="s">
-        <v>166</v>
-      </c>
-      <c r="C5" s="110" t="s">
-        <v>168</v>
-      </c>
-      <c r="D5" s="111"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="111"/>
-      <c r="G5" s="111"/>
-      <c r="H5" s="111"/>
-      <c r="I5" s="106"/>
-    </row>
-    <row r="6" spans="1:9" s="108" customFormat="1" ht="26" x14ac:dyDescent="0.3">
-      <c r="A6" s="107"/>
-      <c r="B6" s="109" t="s">
-        <v>194</v>
-      </c>
-      <c r="C6" s="110" t="s">
-        <v>195</v>
-      </c>
-      <c r="D6" s="111"/>
-      <c r="E6" s="111"/>
-      <c r="F6" s="111"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="111"/>
-      <c r="I6" s="106"/>
-    </row>
-    <row r="7" spans="1:9" s="108" customFormat="1" ht="26" x14ac:dyDescent="0.3">
-      <c r="A7" s="107"/>
-      <c r="B7" s="109" t="s">
-        <v>193</v>
-      </c>
-      <c r="C7" s="110" t="s">
-        <v>196</v>
-      </c>
-      <c r="D7" s="111"/>
-      <c r="E7" s="111"/>
-      <c r="F7" s="111"/>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="106"/>
-    </row>
-    <row r="8" spans="1:9" s="108" customFormat="1" ht="52" x14ac:dyDescent="0.3">
-      <c r="A8" s="107"/>
-      <c r="B8" s="109" t="s">
-        <v>167</v>
-      </c>
-      <c r="C8" s="110" t="s">
-        <v>169</v>
-      </c>
-      <c r="D8" s="134"/>
-      <c r="E8" s="111"/>
-      <c r="F8" s="111"/>
-      <c r="G8" s="111"/>
-      <c r="H8" s="111"/>
-      <c r="I8" s="106"/>
-    </row>
-    <row r="9" spans="1:9" s="129" customFormat="1" ht="26" x14ac:dyDescent="0.3">
-      <c r="A9" s="125" t="s">
-        <v>170</v>
-      </c>
-      <c r="B9" s="126"/>
-      <c r="C9" s="127" t="s">
-        <v>172</v>
-      </c>
-      <c r="D9" s="128"/>
-      <c r="E9" s="128"/>
-      <c r="F9" s="128"/>
-      <c r="G9" s="128"/>
-      <c r="H9" s="128"/>
-      <c r="I9" s="128"/>
-    </row>
-    <row r="10" spans="1:9" s="120" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="117"/>
-      <c r="B10" s="121" t="s">
-        <v>171</v>
-      </c>
-      <c r="C10" s="118" t="s">
-        <v>173</v>
-      </c>
-      <c r="D10" s="122"/>
-      <c r="E10" s="123"/>
-      <c r="F10" s="123"/>
-      <c r="G10" s="123"/>
-      <c r="H10" s="123"/>
-      <c r="I10" s="119"/>
-    </row>
-    <row r="11" spans="1:9" s="120" customFormat="1" ht="26" x14ac:dyDescent="0.3">
-      <c r="A11" s="117"/>
-      <c r="B11" s="121" t="s">
-        <v>174</v>
-      </c>
-      <c r="C11" s="118" t="s">
-        <v>180</v>
-      </c>
-      <c r="D11" s="135"/>
-      <c r="E11" s="136"/>
-      <c r="F11" s="136"/>
-      <c r="G11" s="136"/>
-      <c r="H11" s="123"/>
-      <c r="I11" s="119"/>
-    </row>
-    <row r="12" spans="1:9" s="120" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="117"/>
-      <c r="B12" s="121" t="s">
-        <v>175</v>
-      </c>
-      <c r="C12" s="118"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="123"/>
-      <c r="F12" s="123"/>
-      <c r="G12" s="123"/>
-      <c r="H12" s="123"/>
-      <c r="I12" s="119"/>
-    </row>
-    <row r="13" spans="1:9" s="120" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="117"/>
-      <c r="B13" s="121" t="s">
-        <v>176</v>
-      </c>
-      <c r="C13" s="118"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="123"/>
-      <c r="F13" s="123"/>
-      <c r="G13" s="123"/>
-      <c r="H13" s="123"/>
-      <c r="I13" s="119"/>
-    </row>
-    <row r="14" spans="1:9" s="120" customFormat="1" ht="28" x14ac:dyDescent="0.3">
-      <c r="A14" s="117"/>
-      <c r="B14" s="124" t="s">
-        <v>177</v>
-      </c>
-      <c r="C14" s="118"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="123"/>
-      <c r="F14" s="123"/>
-      <c r="G14" s="123"/>
-      <c r="H14" s="123"/>
-      <c r="I14" s="119"/>
-    </row>
-    <row r="15" spans="1:9" s="120" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="117"/>
-      <c r="B15" s="121" t="s">
-        <v>178</v>
-      </c>
-      <c r="C15" s="118"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="123"/>
-      <c r="F15" s="123"/>
-      <c r="G15" s="123"/>
-      <c r="H15" s="123"/>
-      <c r="I15" s="119"/>
-    </row>
-    <row r="16" spans="1:9" s="120" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="117"/>
-      <c r="B16" s="121" t="s">
-        <v>179</v>
-      </c>
-      <c r="C16" s="118"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="123"/>
-      <c r="F16" s="123"/>
-      <c r="G16" s="123"/>
-      <c r="H16" s="123"/>
-      <c r="I16" s="119"/>
-    </row>
-    <row r="17" spans="1:9" s="120" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="117"/>
-      <c r="B17" s="121" t="s">
-        <v>181</v>
-      </c>
-      <c r="C17" s="118" t="s">
-        <v>183</v>
-      </c>
-      <c r="D17" s="130"/>
-      <c r="E17" s="131"/>
-      <c r="F17" s="131"/>
-      <c r="G17" s="131"/>
-      <c r="H17" s="131"/>
-      <c r="I17" s="119"/>
-    </row>
-    <row r="18" spans="1:9" s="120" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="117"/>
-      <c r="B18" s="121" t="s">
-        <v>182</v>
-      </c>
-      <c r="C18" s="118" t="s">
-        <v>184</v>
-      </c>
-      <c r="D18" s="132"/>
-      <c r="E18" s="133"/>
-      <c r="F18" s="133"/>
-      <c r="G18" s="131"/>
-      <c r="H18" s="131"/>
-      <c r="I18" s="119"/>
-    </row>
-    <row r="19" spans="1:9" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="20" spans="1:9" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:9" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:9" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:9" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:9" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:9" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:9" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:9" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:9" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:9" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:9" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:9" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:9" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="33" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="34" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="35" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="36" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="37" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="38" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="39" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="40" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="41" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="42" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="43" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="44" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="45" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="46" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="47" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="48" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="49" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="50" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="51" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="52" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="53" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="54" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="55" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="56" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="57" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="58" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="59" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="60" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="61" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="62" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="63" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="64" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="65" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="66" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="67" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="68" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="69" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
-        <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C1C4E25D-ABA5-41C3-BED8-BDADE1856557}">
-          <x14:formula1>
-            <xm:f>'Drop Down List Values'!$A$2:$A$7</xm:f>
-          </x14:formula1>
-          <xm:sqref>H11</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5D77A5B3-DC21-4455-8579-74CE8C477205}">
-          <x14:formula1>
-            <xm:f>'Drop Down List Values'!$C$2:$C$5</xm:f>
-          </x14:formula1>
-          <xm:sqref>H13</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{73E3C8C7-4C35-407D-BD90-B3CE9EDEF4AB}">
-          <x14:formula1>
-            <xm:f>'Drop Down List Values'!$B$2:$B$5</xm:f>
-          </x14:formula1>
-          <xm:sqref>H12</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B2DC812E-574B-475E-A423-79EFE715328F}">
-          <x14:formula1>
-            <xm:f>'Drop Down List Values'!N1:N6</xm:f>
-          </x14:formula1>
-          <xm:sqref>D4:H4</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F8BFBD-18C1-4ED5-A02E-9841686C259E}">
   <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -4342,7 +3698,7 @@
         <v>121</v>
       </c>
       <c r="N1" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -4383,10 +3739,10 @@
         <v>136</v>
       </c>
       <c r="M2" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="N2" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
@@ -4427,10 +3783,10 @@
         <v>142</v>
       </c>
       <c r="M3" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="N3" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -4471,10 +3827,10 @@
         <v>152</v>
       </c>
       <c r="M4" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="N4" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -4512,7 +3868,7 @@
         <v>145</v>
       </c>
       <c r="N5" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -4535,7 +3891,7 @@
         <v>160</v>
       </c>
       <c r="N6" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -4559,6 +3915,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">YVWEJ5DVYS2U-421999773-68</_dlc_DocId>
@@ -4572,66 +3937,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008D4902BA52C7D94A994657A564808B2B" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e4455a60d2ff5f5fcd8815d6d89b5b66">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b541edd5-2552-480e-ada6-0e2c8d317108" xmlns:ns3="780ae317-08c5-4e10-af93-dd385a8384a9" xmlns:ns4="3146657c-56f4-4c0a-bb9c-a675121ac670" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1d01ecd782f081d5d944fa263943fc4" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="b541edd5-2552-480e-ada6-0e2c8d317108"/>
@@ -4830,7 +4136,65 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{448710E8-BE9E-4C9E-A40A-0AC1DAE48E99}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E3EF86-6C9E-4C22-A476-13DA012C68C5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -4848,23 +4212,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{448710E8-BE9E-4C9E-A40A-0AC1DAE48E99}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF0D7A6D-D78F-4048-9348-0B4289842B11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0980278E-2A79-4F44-8623-FE545C304BE1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4882,4 +4230,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF0D7A6D-D78F-4048-9348-0B4289842B11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/tests/DCR-JackReacher.xlsx
+++ b/tests/DCR-JackReacher.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mc142/Documents/workspace/mortality-reporting/mdi-import/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069BD54D-DEB1-6548-9CAD-3016E27376C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73613D4B-07B2-0048-BBC4-F098F71DF9BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8340" yWindow="1040" windowWidth="33600" windowHeight="20660" xr2:uid="{7A50F290-1C75-487E-9806-F93553E4E7CC}"/>
+    <workbookView xWindow="960" yWindow="660" windowWidth="33600" windowHeight="20660" xr2:uid="{7A50F290-1C75-487E-9806-F93553E4E7CC}"/>
   </bookViews>
   <sheets>
     <sheet name="DCR" sheetId="4" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="239">
   <si>
     <t>Sections</t>
   </si>
@@ -864,6 +864,15 @@
   <si>
     <t>urn:funeralhome:fulton</t>
   </si>
+  <si>
+    <t>Tracking Number: Funeral Home Case Number</t>
+  </si>
+  <si>
+    <t>A locally unique case number from the funeral home system.</t>
+  </si>
+  <si>
+    <t>24-1021-001</t>
+  </si>
 </sst>
 </file>
 
@@ -872,7 +881,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -951,6 +960,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="22">
@@ -1183,7 +1198,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -1626,6 +1641,14 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2024,7 +2047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54CD1DC7-E143-4CF5-BEA9-4DABBAFFC7B0}">
-  <dimension ref="A1:AU92"/>
+  <dimension ref="A1:AU93"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="21" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.33203125" style="46" customWidth="1"/>
@@ -2131,48 +2154,48 @@
       <c r="H6" s="90"/>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" spans="1:9" s="8" customFormat="1" ht="39" x14ac:dyDescent="0.3">
-      <c r="A7" s="49" t="s">
+    <row r="7" spans="1:9" s="6" customFormat="1" ht="31" x14ac:dyDescent="0.3">
+      <c r="A7" s="48"/>
+      <c r="B7" s="138" t="s">
+        <v>236</v>
+      </c>
+      <c r="C7" s="139" t="s">
+        <v>237</v>
+      </c>
+      <c r="D7" s="90" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="90"/>
+      <c r="F7" s="90"/>
+      <c r="G7" s="90"/>
+      <c r="H7" s="90"/>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="1:9" s="8" customFormat="1" ht="39" x14ac:dyDescent="0.3">
+      <c r="A8" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="125"/>
-      <c r="C7" s="64" t="s">
+      <c r="B8" s="125"/>
+      <c r="C8" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-    </row>
-    <row r="8" spans="1:9" s="11" customFormat="1" ht="78" x14ac:dyDescent="0.3">
-      <c r="A8" s="50"/>
-      <c r="B8" s="59" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="65" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="91" t="s">
-        <v>221</v>
-      </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="10"/>
-    </row>
-    <row r="9" spans="1:9" s="11" customFormat="1" ht="52" x14ac:dyDescent="0.3">
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+    </row>
+    <row r="9" spans="1:9" s="11" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A9" s="50"/>
       <c r="B9" s="59" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C9" s="65" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D9" s="91" t="s">
-        <v>23</v>
+        <v>221</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
@@ -2180,16 +2203,16 @@
       <c r="H9" s="9"/>
       <c r="I9" s="10"/>
     </row>
-    <row r="10" spans="1:9" s="11" customFormat="1" ht="26" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" s="11" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A10" s="50"/>
       <c r="B10" s="59" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C10" s="65" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D10" s="91" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
@@ -2197,16 +2220,16 @@
       <c r="H10" s="9"/>
       <c r="I10" s="10"/>
     </row>
-    <row r="11" spans="1:9" s="11" customFormat="1" ht="39" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" s="11" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A11" s="50"/>
-      <c r="B11" s="126" t="s">
-        <v>27</v>
+      <c r="B11" s="59" t="s">
+        <v>24</v>
       </c>
       <c r="C11" s="65" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D11" s="91" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
@@ -2214,16 +2237,16 @@
       <c r="H11" s="9"/>
       <c r="I11" s="10"/>
     </row>
-    <row r="12" spans="1:9" s="11" customFormat="1" ht="52" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" s="11" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A12" s="50"/>
-      <c r="B12" s="59" t="s">
-        <v>30</v>
+      <c r="B12" s="126" t="s">
+        <v>27</v>
       </c>
       <c r="C12" s="65" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D12" s="91" t="s">
-        <v>193</v>
+        <v>29</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
@@ -2231,16 +2254,16 @@
       <c r="H12" s="9"/>
       <c r="I12" s="10"/>
     </row>
-    <row r="13" spans="1:9" s="11" customFormat="1" ht="65" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" s="11" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A13" s="50"/>
       <c r="B13" s="59" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C13" s="65" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="91">
-        <v>45</v>
+        <v>31</v>
+      </c>
+      <c r="D13" s="91" t="s">
+        <v>193</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
@@ -2248,60 +2271,64 @@
       <c r="H13" s="9"/>
       <c r="I13" s="10"/>
     </row>
-    <row r="14" spans="1:9" s="11" customFormat="1" ht="52" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" s="11" customFormat="1" ht="65" x14ac:dyDescent="0.3">
       <c r="A14" s="50"/>
       <c r="B14" s="59" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C14" s="65" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="93">
-        <v>28561</v>
-      </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
+        <v>33</v>
+      </c>
+      <c r="D14" s="91">
+        <v>45</v>
+      </c>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
       <c r="I14" s="10"/>
     </row>
-    <row r="15" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" s="11" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A15" s="50"/>
       <c r="B15" s="59" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="65"/>
-      <c r="D15" s="91"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+        <v>34</v>
+      </c>
+      <c r="C15" s="65" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="93">
+        <v>28561</v>
+      </c>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
       <c r="I15" s="10"/>
     </row>
-    <row r="16" spans="1:9" s="11" customFormat="1" ht="26" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="50"/>
       <c r="B16" s="59" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="65" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="106"/>
-      <c r="E16" s="107"/>
-      <c r="F16" s="107"/>
+        <v>36</v>
+      </c>
+      <c r="C16" s="65"/>
+      <c r="D16" s="91"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
       <c r="I16" s="10"/>
     </row>
-    <row r="17" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="11" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A17" s="50"/>
       <c r="B17" s="59" t="s">
-        <v>170</v>
-      </c>
-      <c r="C17" s="65"/>
-      <c r="D17" s="91"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
+        <v>37</v>
+      </c>
+      <c r="C17" s="65" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="106"/>
+      <c r="E17" s="107"/>
+      <c r="F17" s="107"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="10"/>
@@ -2309,7 +2336,7 @@
     <row r="18" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="50"/>
       <c r="B18" s="59" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C18" s="65"/>
       <c r="D18" s="91"/>
@@ -2319,10 +2346,10 @@
       <c r="H18" s="9"/>
       <c r="I18" s="10"/>
     </row>
-    <row r="19" spans="1:9" s="11" customFormat="1" ht="28" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="50"/>
       <c r="B19" s="59" t="s">
-        <v>39</v>
+        <v>171</v>
       </c>
       <c r="C19" s="65"/>
       <c r="D19" s="91"/>
@@ -2332,10 +2359,10 @@
       <c r="H19" s="9"/>
       <c r="I19" s="10"/>
     </row>
-    <row r="20" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="11" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A20" s="50"/>
       <c r="B20" s="59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" s="65"/>
       <c r="D20" s="91"/>
@@ -2348,7 +2375,7 @@
     <row r="21" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="50"/>
       <c r="B21" s="59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C21" s="65"/>
       <c r="D21" s="91"/>
@@ -2358,73 +2385,71 @@
       <c r="H21" s="9"/>
       <c r="I21" s="10"/>
     </row>
-    <row r="22" spans="1:9" s="13" customFormat="1" ht="91" x14ac:dyDescent="0.3">
-      <c r="A22" s="75" t="s">
+    <row r="22" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="50"/>
+      <c r="B22" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="65"/>
+      <c r="D22" s="91"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="10"/>
+    </row>
+    <row r="23" spans="1:9" s="13" customFormat="1" ht="91" x14ac:dyDescent="0.3">
+      <c r="A23" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="127"/>
-      <c r="C22" s="66" t="s">
+      <c r="B23" s="127"/>
+      <c r="C23" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="92"/>
-      <c r="E22" s="92"/>
-      <c r="F22" s="92"/>
-      <c r="G22" s="92"/>
-      <c r="H22" s="92"/>
-      <c r="I22" s="92"/>
-    </row>
-    <row r="23" spans="1:9" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="51"/>
-      <c r="B23" s="80" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="99"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="83"/>
-      <c r="G23" s="83"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15"/>
+      <c r="D23" s="92"/>
+      <c r="E23" s="92"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="92"/>
+      <c r="H23" s="92"/>
+      <c r="I23" s="92"/>
     </row>
     <row r="24" spans="1:9" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="51"/>
       <c r="B24" s="80" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C24" s="67" t="s">
-        <v>47</v>
-      </c>
-      <c r="D24" s="95"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="84"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
+        <v>45</v>
+      </c>
+      <c r="D24" s="99"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="83"/>
+      <c r="H24" s="14"/>
       <c r="I24" s="15"/>
     </row>
     <row r="25" spans="1:9" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="51"/>
       <c r="B25" s="80" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C25" s="67" t="s">
-        <v>49</v>
-      </c>
-      <c r="D25" s="96"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
+        <v>47</v>
+      </c>
+      <c r="D25" s="95"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="84"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
       <c r="I25" s="15"/>
     </row>
     <row r="26" spans="1:9" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="51"/>
       <c r="B26" s="80" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C26" s="67" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D26" s="96"/>
       <c r="E26" s="18"/>
@@ -2433,13 +2458,13 @@
       <c r="H26" s="18"/>
       <c r="I26" s="15"/>
     </row>
-    <row r="27" spans="1:9" s="16" customFormat="1" ht="52" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="51"/>
       <c r="B27" s="80" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C27" s="67" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D27" s="96"/>
       <c r="E27" s="18"/>
@@ -2451,10 +2476,10 @@
     <row r="28" spans="1:9" s="16" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A28" s="51"/>
       <c r="B28" s="80" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C28" s="67" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D28" s="96"/>
       <c r="E28" s="18"/>
@@ -2466,10 +2491,10 @@
     <row r="29" spans="1:9" s="16" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A29" s="51"/>
       <c r="B29" s="80" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C29" s="67" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D29" s="96"/>
       <c r="E29" s="18"/>
@@ -2481,115 +2506,115 @@
     <row r="30" spans="1:9" s="16" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A30" s="51"/>
       <c r="B30" s="80" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C30" s="67" t="s">
-        <v>59</v>
-      </c>
-      <c r="D30" s="94"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
+        <v>57</v>
+      </c>
+      <c r="D30" s="96"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
       <c r="I30" s="15"/>
     </row>
-    <row r="31" spans="1:9" s="16" customFormat="1" ht="39" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" s="16" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A31" s="51"/>
       <c r="B31" s="80" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" s="67" t="s">
+        <v>59</v>
+      </c>
+      <c r="D31" s="94"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="15"/>
+    </row>
+    <row r="32" spans="1:9" s="16" customFormat="1" ht="39" x14ac:dyDescent="0.3">
+      <c r="A32" s="51"/>
+      <c r="B32" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="67" t="s">
+      <c r="C32" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="D31" s="96"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="15"/>
-    </row>
-    <row r="32" spans="1:9" s="16" customFormat="1" ht="26" x14ac:dyDescent="0.3">
-      <c r="A32" s="51"/>
-      <c r="B32" s="60" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" s="67" t="s">
-        <v>63</v>
-      </c>
-      <c r="D32" s="97"/>
-      <c r="E32" s="19"/>
+      <c r="D32" s="96"/>
+      <c r="E32" s="18"/>
       <c r="F32" s="19"/>
       <c r="G32" s="19"/>
       <c r="H32" s="19"/>
       <c r="I32" s="15"/>
     </row>
-    <row r="33" spans="1:9" s="16" customFormat="1" ht="65" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" s="16" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A33" s="51"/>
       <c r="B33" s="60" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C33" s="67" t="s">
-        <v>66</v>
-      </c>
-      <c r="D33" s="98"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
+        <v>63</v>
+      </c>
+      <c r="D33" s="97"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
       <c r="I33" s="15"/>
     </row>
-    <row r="34" spans="1:9" s="16" customFormat="1" ht="91" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" s="16" customFormat="1" ht="65" x14ac:dyDescent="0.3">
       <c r="A34" s="51"/>
       <c r="B34" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" s="67" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" s="98"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="15"/>
+    </row>
+    <row r="35" spans="1:9" s="16" customFormat="1" ht="91" x14ac:dyDescent="0.3">
+      <c r="A35" s="51"/>
+      <c r="B35" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="67" t="s">
+      <c r="C35" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="D34" s="100"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="85"/>
-      <c r="G34" s="21"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="15"/>
-    </row>
-    <row r="35" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="52"/>
-      <c r="B35" s="60" t="s">
+      <c r="D35" s="100"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="85"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="15"/>
+    </row>
+    <row r="36" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="52"/>
+      <c r="B36" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="C35" s="67" t="s">
+      <c r="C36" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="D35" s="96"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="22"/>
-    </row>
-    <row r="36" spans="1:9" s="16" customFormat="1" ht="39" x14ac:dyDescent="0.3">
-      <c r="A36" s="51"/>
-      <c r="B36" s="60" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" s="67" t="s">
-        <v>72</v>
-      </c>
-      <c r="D36" s="97"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="15"/>
+      <c r="D36" s="96"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="22"/>
     </row>
     <row r="37" spans="1:9" s="16" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A37" s="51"/>
       <c r="B37" s="60" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C37" s="67" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D37" s="97"/>
       <c r="E37" s="19"/>
@@ -2598,46 +2623,46 @@
       <c r="H37" s="19"/>
       <c r="I37" s="15"/>
     </row>
-    <row r="38" spans="1:9" s="25" customFormat="1" ht="91" x14ac:dyDescent="0.3">
-      <c r="A38" s="76" t="s">
+    <row r="38" spans="1:9" s="16" customFormat="1" ht="39" x14ac:dyDescent="0.3">
+      <c r="A38" s="51"/>
+      <c r="B38" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="67" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38" s="97"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="15"/>
+    </row>
+    <row r="39" spans="1:9" s="25" customFormat="1" ht="91" x14ac:dyDescent="0.3">
+      <c r="A39" s="76" t="s">
         <v>76</v>
       </c>
-      <c r="B38" s="128"/>
-      <c r="C38" s="68" t="s">
+      <c r="B39" s="128"/>
+      <c r="C39" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="24"/>
-      <c r="H38" s="24"/>
-      <c r="I38" s="24"/>
-    </row>
-    <row r="39" spans="1:9" s="28" customFormat="1" ht="26" x14ac:dyDescent="0.3">
-      <c r="A39" s="53"/>
-      <c r="B39" s="77" t="s">
-        <v>172</v>
-      </c>
-      <c r="C39" s="69" t="s">
-        <v>173</v>
-      </c>
-      <c r="D39" s="102" t="s">
-        <v>181</v>
-      </c>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="27"/>
-    </row>
-    <row r="40" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="24"/>
+    </row>
+    <row r="40" spans="1:9" s="28" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A40" s="53"/>
       <c r="B40" s="77" t="s">
-        <v>174</v>
-      </c>
-      <c r="C40" s="69"/>
+        <v>172</v>
+      </c>
+      <c r="C40" s="69" t="s">
+        <v>173</v>
+      </c>
       <c r="D40" s="102" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E40" s="26"/>
       <c r="F40" s="26"/>
@@ -2648,39 +2673,39 @@
     <row r="41" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="53"/>
       <c r="B41" s="77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C41" s="69"/>
-      <c r="D41" s="102"/>
+      <c r="D41" s="102" t="s">
+        <v>182</v>
+      </c>
       <c r="E41" s="26"/>
       <c r="F41" s="26"/>
       <c r="G41" s="26"/>
       <c r="H41" s="26"/>
       <c r="I41" s="27"/>
     </row>
-    <row r="42" spans="1:9" s="28" customFormat="1" ht="28" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="53"/>
       <c r="B42" s="77" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C42" s="69"/>
-      <c r="D42" s="102" t="s">
-        <v>183</v>
-      </c>
+      <c r="D42" s="102"/>
       <c r="E42" s="26"/>
       <c r="F42" s="26"/>
       <c r="G42" s="26"/>
       <c r="H42" s="26"/>
       <c r="I42" s="27"/>
     </row>
-    <row r="43" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" s="28" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A43" s="53"/>
       <c r="B43" s="77" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C43" s="69"/>
-      <c r="D43" s="102">
-        <v>90909</v>
+      <c r="D43" s="102" t="s">
+        <v>183</v>
       </c>
       <c r="E43" s="26"/>
       <c r="F43" s="26"/>
@@ -2691,11 +2716,11 @@
     <row r="44" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="53"/>
       <c r="B44" s="77" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C44" s="69"/>
-      <c r="D44" s="108" t="s">
-        <v>204</v>
+      <c r="D44" s="102">
+        <v>90909</v>
       </c>
       <c r="E44" s="26"/>
       <c r="F44" s="26"/>
@@ -2703,31 +2728,31 @@
       <c r="H44" s="26"/>
       <c r="I44" s="27"/>
     </row>
-    <row r="45" spans="1:9" s="28" customFormat="1" ht="26" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="53"/>
-      <c r="B45" s="129" t="s">
-        <v>184</v>
-      </c>
-      <c r="C45" s="69" t="s">
-        <v>185</v>
-      </c>
-      <c r="D45" s="102" t="s">
-        <v>191</v>
-      </c>
-      <c r="E45" s="109"/>
+      <c r="B45" s="77" t="s">
+        <v>178</v>
+      </c>
+      <c r="C45" s="69"/>
+      <c r="D45" s="108" t="s">
+        <v>204</v>
+      </c>
+      <c r="E45" s="26"/>
       <c r="F45" s="26"/>
-      <c r="G45" s="109"/>
-      <c r="H45" s="109"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="26"/>
       <c r="I45" s="27"/>
     </row>
-    <row r="46" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" s="28" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A46" s="53"/>
       <c r="B46" s="129" t="s">
-        <v>186</v>
-      </c>
-      <c r="C46" s="69"/>
+        <v>184</v>
+      </c>
+      <c r="C46" s="69" t="s">
+        <v>185</v>
+      </c>
       <c r="D46" s="102" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E46" s="109"/>
       <c r="F46" s="26"/>
@@ -2738,39 +2763,39 @@
     <row r="47" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="53"/>
       <c r="B47" s="129" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C47" s="69"/>
-      <c r="D47" s="102"/>
+      <c r="D47" s="102" t="s">
+        <v>192</v>
+      </c>
       <c r="E47" s="109"/>
       <c r="F47" s="26"/>
       <c r="G47" s="109"/>
       <c r="H47" s="109"/>
       <c r="I47" s="27"/>
     </row>
-    <row r="48" spans="1:9" s="28" customFormat="1" ht="28" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="53"/>
       <c r="B48" s="129" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C48" s="69"/>
-      <c r="D48" s="102" t="s">
-        <v>183</v>
-      </c>
+      <c r="D48" s="102"/>
       <c r="E48" s="109"/>
       <c r="F48" s="26"/>
       <c r="G48" s="109"/>
       <c r="H48" s="109"/>
       <c r="I48" s="27"/>
     </row>
-    <row r="49" spans="1:47" s="28" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" s="28" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A49" s="53"/>
       <c r="B49" s="129" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C49" s="69"/>
-      <c r="D49" s="102">
-        <v>30445</v>
+      <c r="D49" s="102" t="s">
+        <v>183</v>
       </c>
       <c r="E49" s="109"/>
       <c r="F49" s="26"/>
@@ -2778,197 +2803,197 @@
       <c r="H49" s="109"/>
       <c r="I49" s="27"/>
     </row>
-    <row r="50" spans="1:47" s="28" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="53"/>
       <c r="B50" s="129" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C50" s="69"/>
-      <c r="D50" s="102"/>
+      <c r="D50" s="102">
+        <v>30445</v>
+      </c>
       <c r="E50" s="109"/>
       <c r="F50" s="26"/>
       <c r="G50" s="109"/>
       <c r="H50" s="109"/>
       <c r="I50" s="27"/>
     </row>
-    <row r="51" spans="1:47" s="28" customFormat="1" ht="39" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="53"/>
-      <c r="B51" s="77" t="s">
-        <v>78</v>
-      </c>
-      <c r="C51" s="69" t="s">
-        <v>79</v>
-      </c>
+      <c r="B51" s="129" t="s">
+        <v>190</v>
+      </c>
+      <c r="C51" s="69"/>
       <c r="D51" s="102"/>
-      <c r="E51" s="102"/>
-      <c r="F51" s="102"/>
-      <c r="G51" s="102"/>
-      <c r="H51" s="102"/>
+      <c r="E51" s="109"/>
+      <c r="F51" s="26"/>
+      <c r="G51" s="109"/>
+      <c r="H51" s="109"/>
       <c r="I51" s="27"/>
     </row>
-    <row r="52" spans="1:47" s="28" customFormat="1" ht="39" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" s="28" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A52" s="53"/>
       <c r="B52" s="77" t="s">
+        <v>78</v>
+      </c>
+      <c r="C52" s="69" t="s">
+        <v>79</v>
+      </c>
+      <c r="D52" s="102"/>
+      <c r="E52" s="102"/>
+      <c r="F52" s="102"/>
+      <c r="G52" s="102"/>
+      <c r="H52" s="102"/>
+      <c r="I52" s="27"/>
+    </row>
+    <row r="53" spans="1:9" s="28" customFormat="1" ht="39" x14ac:dyDescent="0.3">
+      <c r="A53" s="53"/>
+      <c r="B53" s="77" t="s">
         <v>81</v>
       </c>
-      <c r="C52" s="69" t="s">
+      <c r="C53" s="69" t="s">
         <v>82</v>
       </c>
-      <c r="D52" s="102"/>
-      <c r="E52" s="26"/>
-      <c r="F52" s="26"/>
-      <c r="G52" s="26"/>
-      <c r="H52" s="26"/>
-      <c r="I52" s="27"/>
-    </row>
-    <row r="53" spans="1:47" s="31" customFormat="1" ht="65" x14ac:dyDescent="0.3">
-      <c r="A53" s="82" t="s">
+      <c r="D53" s="102"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
+      <c r="G53" s="26"/>
+      <c r="H53" s="26"/>
+      <c r="I53" s="27"/>
+    </row>
+    <row r="54" spans="1:9" s="31" customFormat="1" ht="65" x14ac:dyDescent="0.3">
+      <c r="A54" s="82" t="s">
         <v>83</v>
       </c>
-      <c r="B53" s="130"/>
-      <c r="C53" s="70" t="s">
+      <c r="B54" s="130"/>
+      <c r="C54" s="70" t="s">
         <v>84</v>
       </c>
-      <c r="D53" s="103"/>
-      <c r="E53" s="29"/>
-      <c r="F53" s="29"/>
-      <c r="G53" s="29"/>
-      <c r="H53" s="29"/>
-      <c r="I53" s="30"/>
-    </row>
-    <row r="54" spans="1:47" s="34" customFormat="1" ht="52" x14ac:dyDescent="0.3">
-      <c r="A54" s="54"/>
-      <c r="B54" s="131" t="s">
-        <v>85</v>
-      </c>
-      <c r="C54" s="71" t="s">
-        <v>86</v>
-      </c>
-      <c r="D54" s="32" t="s">
-        <v>179</v>
-      </c>
-      <c r="E54" s="32"/>
-      <c r="F54" s="32"/>
-      <c r="G54" s="32"/>
-      <c r="H54" s="32"/>
-      <c r="I54" s="33"/>
-    </row>
-    <row r="55" spans="1:47" s="34" customFormat="1" ht="91" x14ac:dyDescent="0.3">
+      <c r="D54" s="103"/>
+      <c r="E54" s="29"/>
+      <c r="F54" s="29"/>
+      <c r="G54" s="29"/>
+      <c r="H54" s="29"/>
+      <c r="I54" s="30"/>
+    </row>
+    <row r="55" spans="1:9" s="34" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A55" s="54"/>
       <c r="B55" s="131" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C55" s="71" t="s">
-        <v>88</v>
-      </c>
-      <c r="D55" s="35" t="s">
-        <v>180</v>
-      </c>
-      <c r="E55" s="35"/>
-      <c r="F55" s="35"/>
-      <c r="G55" s="35"/>
-      <c r="H55" s="35"/>
+        <v>86</v>
+      </c>
+      <c r="D55" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
       <c r="I55" s="33"/>
     </row>
-    <row r="56" spans="1:47" s="34" customFormat="1" ht="39" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" s="34" customFormat="1" ht="91" x14ac:dyDescent="0.3">
       <c r="A56" s="54"/>
       <c r="B56" s="131" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C56" s="71" t="s">
-        <v>90</v>
-      </c>
-      <c r="D56" s="101"/>
-      <c r="E56" s="101"/>
-      <c r="F56" s="101"/>
-      <c r="G56" s="101"/>
-      <c r="H56" s="101"/>
+        <v>88</v>
+      </c>
+      <c r="D56" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="E56" s="35"/>
+      <c r="F56" s="35"/>
+      <c r="G56" s="35"/>
+      <c r="H56" s="35"/>
       <c r="I56" s="33"/>
     </row>
-    <row r="57" spans="1:47" s="34" customFormat="1" ht="65" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" s="34" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A57" s="54"/>
       <c r="B57" s="131" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C57" s="71" t="s">
-        <v>93</v>
-      </c>
-      <c r="D57" s="36"/>
-      <c r="E57" s="36"/>
-      <c r="F57" s="36"/>
-      <c r="G57" s="36"/>
-      <c r="H57" s="36"/>
+        <v>90</v>
+      </c>
+      <c r="D57" s="101"/>
+      <c r="E57" s="101"/>
+      <c r="F57" s="101"/>
+      <c r="G57" s="101"/>
+      <c r="H57" s="101"/>
       <c r="I57" s="33"/>
     </row>
-    <row r="58" spans="1:47" s="34" customFormat="1" ht="91" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" s="34" customFormat="1" ht="65" x14ac:dyDescent="0.3">
       <c r="A58" s="54"/>
       <c r="B58" s="131" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C58" s="71" t="s">
-        <v>95</v>
-      </c>
-      <c r="D58" s="35"/>
-      <c r="E58" s="35"/>
-      <c r="F58" s="35"/>
-      <c r="G58" s="35"/>
-      <c r="H58" s="35"/>
+        <v>93</v>
+      </c>
+      <c r="D58" s="36"/>
+      <c r="E58" s="36"/>
+      <c r="F58" s="36"/>
+      <c r="G58" s="36"/>
+      <c r="H58" s="36"/>
       <c r="I58" s="33"/>
     </row>
-    <row r="59" spans="1:47" s="34" customFormat="1" ht="39" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" s="34" customFormat="1" ht="91" x14ac:dyDescent="0.3">
       <c r="A59" s="54"/>
       <c r="B59" s="131" t="s">
+        <v>94</v>
+      </c>
+      <c r="C59" s="71" t="s">
+        <v>95</v>
+      </c>
+      <c r="D59" s="35"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="35"/>
+      <c r="H59" s="35"/>
+      <c r="I59" s="33"/>
+    </row>
+    <row r="60" spans="1:9" s="34" customFormat="1" ht="39" x14ac:dyDescent="0.3">
+      <c r="A60" s="54"/>
+      <c r="B60" s="131" t="s">
         <v>96</v>
       </c>
-      <c r="C59" s="71" t="s">
+      <c r="C60" s="71" t="s">
         <v>97</v>
       </c>
-      <c r="D59" s="101" t="s">
+      <c r="D60" s="101" t="s">
         <v>140</v>
       </c>
-      <c r="E59" s="101"/>
-      <c r="F59" s="101"/>
-      <c r="G59" s="101"/>
-      <c r="H59" s="101"/>
-      <c r="I59" s="33"/>
-    </row>
-    <row r="60" spans="1:47" s="38" customFormat="1" ht="26" x14ac:dyDescent="0.3">
-      <c r="A60" s="55" t="s">
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="33"/>
+    </row>
+    <row r="61" spans="1:9" s="38" customFormat="1" ht="26" x14ac:dyDescent="0.3">
+      <c r="A61" s="55" t="s">
         <v>99</v>
       </c>
-      <c r="B60" s="132"/>
-      <c r="C60" s="72" t="s">
+      <c r="B61" s="132"/>
+      <c r="C61" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="D60" s="37"/>
-      <c r="E60" s="37"/>
-      <c r="F60" s="37"/>
-      <c r="G60" s="37"/>
-      <c r="H60" s="37"/>
-      <c r="I60" s="37"/>
-    </row>
-    <row r="61" spans="1:47" s="41" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="56"/>
-      <c r="B61" s="133" t="s">
-        <v>101</v>
-      </c>
-      <c r="C61" s="73" t="s">
-        <v>102</v>
-      </c>
-      <c r="D61" s="104"/>
-      <c r="E61" s="39"/>
-      <c r="F61" s="39"/>
-      <c r="G61" s="39"/>
-      <c r="H61" s="39"/>
-      <c r="I61" s="40"/>
-    </row>
-    <row r="62" spans="1:47" s="41" customFormat="1" ht="26" x14ac:dyDescent="0.3">
+      <c r="D61" s="37"/>
+      <c r="E61" s="37"/>
+      <c r="F61" s="37"/>
+      <c r="G61" s="37"/>
+      <c r="H61" s="37"/>
+      <c r="I61" s="37"/>
+    </row>
+    <row r="62" spans="1:9" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="56"/>
       <c r="B62" s="133" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C62" s="73" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D62" s="104"/>
       <c r="E62" s="39"/>
@@ -2977,28 +3002,28 @@
       <c r="H62" s="39"/>
       <c r="I62" s="40"/>
     </row>
-    <row r="63" spans="1:47" s="41" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" s="41" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A63" s="56"/>
       <c r="B63" s="133" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C63" s="73" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D63" s="104"/>
-      <c r="E63" s="104"/>
-      <c r="F63" s="104"/>
-      <c r="G63" s="104"/>
-      <c r="H63" s="104"/>
-      <c r="I63" s="56"/>
-    </row>
-    <row r="64" spans="1:47" s="42" customFormat="1" ht="26" x14ac:dyDescent="0.3">
+      <c r="E63" s="39"/>
+      <c r="F63" s="39"/>
+      <c r="G63" s="39"/>
+      <c r="H63" s="39"/>
+      <c r="I63" s="40"/>
+    </row>
+    <row r="64" spans="1:9" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="56"/>
       <c r="B64" s="133" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C64" s="73" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D64" s="104"/>
       <c r="E64" s="104"/>
@@ -3006,51 +3031,15 @@
       <c r="G64" s="104"/>
       <c r="H64" s="104"/>
       <c r="I64" s="56"/>
-      <c r="J64" s="56"/>
-      <c r="K64" s="56"/>
-      <c r="L64" s="56"/>
-      <c r="M64" s="56"/>
-      <c r="N64" s="56"/>
-      <c r="O64" s="56"/>
-      <c r="P64" s="56"/>
-      <c r="Q64" s="56"/>
-      <c r="R64" s="56"/>
-      <c r="S64" s="56"/>
-      <c r="T64" s="56"/>
-      <c r="U64" s="56"/>
-      <c r="V64" s="56"/>
-      <c r="W64" s="56"/>
-      <c r="X64" s="56"/>
-      <c r="Y64" s="56"/>
-      <c r="Z64" s="56"/>
-      <c r="AA64" s="56"/>
-      <c r="AB64" s="56"/>
-      <c r="AC64" s="56"/>
-      <c r="AD64" s="56"/>
-      <c r="AE64" s="56"/>
-      <c r="AF64" s="56"/>
-      <c r="AG64" s="56"/>
-      <c r="AH64" s="56"/>
-      <c r="AI64" s="56"/>
-      <c r="AJ64" s="56"/>
-      <c r="AK64" s="56"/>
-      <c r="AL64" s="56"/>
-      <c r="AM64" s="56"/>
-      <c r="AN64" s="56"/>
-      <c r="AO64" s="56"/>
-      <c r="AP64" s="56"/>
-      <c r="AQ64" s="56"/>
-      <c r="AR64" s="56"/>
-      <c r="AS64" s="56"/>
-      <c r="AT64" s="56"/>
-      <c r="AU64" s="56"/>
-    </row>
-    <row r="65" spans="1:47" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:47" s="42" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A65" s="56"/>
       <c r="B65" s="133" t="s">
-        <v>109</v>
-      </c>
-      <c r="C65" s="73"/>
+        <v>107</v>
+      </c>
+      <c r="C65" s="73" t="s">
+        <v>108</v>
+      </c>
       <c r="D65" s="104"/>
       <c r="E65" s="104"/>
       <c r="F65" s="104"/>
@@ -3096,10 +3085,10 @@
       <c r="AT65" s="56"/>
       <c r="AU65" s="56"/>
     </row>
-    <row r="66" spans="1:47" s="45" customFormat="1" ht="28" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:47" s="45" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="56"/>
       <c r="B66" s="133" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C66" s="73"/>
       <c r="D66" s="104"/>
@@ -3150,7 +3139,7 @@
     <row r="67" spans="1:47" s="45" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A67" s="56"/>
       <c r="B67" s="133" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C67" s="73"/>
       <c r="D67" s="104"/>
@@ -3201,7 +3190,7 @@
     <row r="68" spans="1:47" s="45" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A68" s="56"/>
       <c r="B68" s="133" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C68" s="73"/>
       <c r="D68" s="104"/>
@@ -3249,51 +3238,89 @@
       <c r="AT68" s="56"/>
       <c r="AU68" s="56"/>
     </row>
-    <row r="69" spans="1:47" s="89" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="86" t="s">
+    <row r="69" spans="1:47" s="45" customFormat="1" ht="28" x14ac:dyDescent="0.3">
+      <c r="A69" s="56"/>
+      <c r="B69" s="133" t="s">
+        <v>112</v>
+      </c>
+      <c r="C69" s="73"/>
+      <c r="D69" s="104"/>
+      <c r="E69" s="104"/>
+      <c r="F69" s="104"/>
+      <c r="G69" s="104"/>
+      <c r="H69" s="104"/>
+      <c r="I69" s="56"/>
+      <c r="J69" s="56"/>
+      <c r="K69" s="56"/>
+      <c r="L69" s="56"/>
+      <c r="M69" s="56"/>
+      <c r="N69" s="56"/>
+      <c r="O69" s="56"/>
+      <c r="P69" s="56"/>
+      <c r="Q69" s="56"/>
+      <c r="R69" s="56"/>
+      <c r="S69" s="56"/>
+      <c r="T69" s="56"/>
+      <c r="U69" s="56"/>
+      <c r="V69" s="56"/>
+      <c r="W69" s="56"/>
+      <c r="X69" s="56"/>
+      <c r="Y69" s="56"/>
+      <c r="Z69" s="56"/>
+      <c r="AA69" s="56"/>
+      <c r="AB69" s="56"/>
+      <c r="AC69" s="56"/>
+      <c r="AD69" s="56"/>
+      <c r="AE69" s="56"/>
+      <c r="AF69" s="56"/>
+      <c r="AG69" s="56"/>
+      <c r="AH69" s="56"/>
+      <c r="AI69" s="56"/>
+      <c r="AJ69" s="56"/>
+      <c r="AK69" s="56"/>
+      <c r="AL69" s="56"/>
+      <c r="AM69" s="56"/>
+      <c r="AN69" s="56"/>
+      <c r="AO69" s="56"/>
+      <c r="AP69" s="56"/>
+      <c r="AQ69" s="56"/>
+      <c r="AR69" s="56"/>
+      <c r="AS69" s="56"/>
+      <c r="AT69" s="56"/>
+      <c r="AU69" s="56"/>
+    </row>
+    <row r="70" spans="1:47" s="89" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="86" t="s">
         <v>163</v>
       </c>
-      <c r="B69" s="134"/>
-      <c r="C69" s="87"/>
-      <c r="D69" s="88"/>
-      <c r="E69" s="88"/>
-      <c r="F69" s="88"/>
-      <c r="G69" s="88"/>
-      <c r="H69" s="88"/>
-      <c r="I69" s="88"/>
-    </row>
-    <row r="70" spans="1:47" s="45" customFormat="1" ht="26" x14ac:dyDescent="0.3">
-      <c r="A70" s="57"/>
-      <c r="B70" s="61" t="s">
-        <v>113</v>
-      </c>
-      <c r="C70" s="74" t="s">
-        <v>114</v>
-      </c>
-      <c r="D70" s="105"/>
-      <c r="E70" s="105"/>
-      <c r="F70" s="105"/>
-      <c r="G70" s="105"/>
-      <c r="H70" s="43"/>
-      <c r="I70" s="44"/>
-    </row>
-    <row r="71" spans="1:47" s="45" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="134"/>
+      <c r="C70" s="87"/>
+      <c r="D70" s="88"/>
+      <c r="E70" s="88"/>
+      <c r="F70" s="88"/>
+      <c r="G70" s="88"/>
+      <c r="H70" s="88"/>
+      <c r="I70" s="88"/>
+    </row>
+    <row r="71" spans="1:47" s="45" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A71" s="57"/>
       <c r="B71" s="61" t="s">
-        <v>115</v>
-      </c>
-      <c r="C71" s="74"/>
+        <v>113</v>
+      </c>
+      <c r="C71" s="74" t="s">
+        <v>114</v>
+      </c>
       <c r="D71" s="105"/>
-      <c r="E71" s="43"/>
-      <c r="F71" s="43"/>
-      <c r="G71" s="43"/>
+      <c r="E71" s="105"/>
+      <c r="F71" s="105"/>
+      <c r="G71" s="105"/>
       <c r="H71" s="43"/>
       <c r="I71" s="44"/>
     </row>
     <row r="72" spans="1:47" s="45" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="57"/>
       <c r="B72" s="61" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C72" s="74"/>
       <c r="D72" s="105"/>
@@ -3303,10 +3330,10 @@
       <c r="H72" s="43"/>
       <c r="I72" s="44"/>
     </row>
-    <row r="73" spans="1:47" s="45" customFormat="1" ht="28" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:47" s="45" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="57"/>
       <c r="B73" s="61" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C73" s="74"/>
       <c r="D73" s="105"/>
@@ -3319,7 +3346,7 @@
     <row r="74" spans="1:47" s="45" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A74" s="57"/>
       <c r="B74" s="61" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C74" s="74"/>
       <c r="D74" s="105"/>
@@ -3329,33 +3356,29 @@
       <c r="H74" s="43"/>
       <c r="I74" s="44"/>
     </row>
-    <row r="75" spans="1:47" s="45" customFormat="1" ht="78" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:47" s="45" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A75" s="57"/>
       <c r="B75" s="61" t="s">
-        <v>119</v>
-      </c>
-      <c r="C75" s="74" t="s">
-        <v>120</v>
-      </c>
-      <c r="D75" s="105" t="s">
-        <v>205</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="C75" s="74"/>
+      <c r="D75" s="105"/>
       <c r="E75" s="43"/>
       <c r="F75" s="43"/>
       <c r="G75" s="43"/>
       <c r="H75" s="43"/>
       <c r="I75" s="44"/>
     </row>
-    <row r="76" spans="1:47" s="45" customFormat="1" ht="26" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:47" s="45" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A76" s="57"/>
       <c r="B76" s="61" t="s">
-        <v>197</v>
+        <v>119</v>
       </c>
       <c r="C76" s="74" t="s">
-        <v>198</v>
+        <v>120</v>
       </c>
       <c r="D76" s="105" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E76" s="43"/>
       <c r="F76" s="43"/>
@@ -3363,16 +3386,16 @@
       <c r="H76" s="43"/>
       <c r="I76" s="44"/>
     </row>
-    <row r="77" spans="1:47" s="45" customFormat="1" ht="39" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:47" s="45" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A77" s="57"/>
       <c r="B77" s="61" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C77" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="D77" s="105">
-        <v>7890123456</v>
+        <v>198</v>
+      </c>
+      <c r="D77" s="105" t="s">
+        <v>203</v>
       </c>
       <c r="E77" s="43"/>
       <c r="F77" s="43"/>
@@ -3380,16 +3403,16 @@
       <c r="H77" s="43"/>
       <c r="I77" s="44"/>
     </row>
-    <row r="78" spans="1:47" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:47" s="45" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A78" s="57"/>
       <c r="B78" s="61" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C78" s="74" t="s">
-        <v>202</v>
-      </c>
-      <c r="D78" s="110">
-        <v>45340</v>
+        <v>200</v>
+      </c>
+      <c r="D78" s="105">
+        <v>7890123456</v>
       </c>
       <c r="E78" s="43"/>
       <c r="F78" s="43"/>
@@ -3400,13 +3423,13 @@
     <row r="79" spans="1:47" s="45" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" s="57"/>
       <c r="B79" s="61" t="s">
-        <v>121</v>
+        <v>201</v>
       </c>
       <c r="C79" s="74" t="s">
-        <v>122</v>
-      </c>
-      <c r="D79" s="105" t="s">
-        <v>194</v>
+        <v>202</v>
+      </c>
+      <c r="D79" s="110">
+        <v>45340</v>
       </c>
       <c r="E79" s="43"/>
       <c r="F79" s="43"/>
@@ -3414,46 +3437,46 @@
       <c r="H79" s="43"/>
       <c r="I79" s="44"/>
     </row>
-    <row r="80" spans="1:47" s="114" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="111" t="s">
+    <row r="80" spans="1:47" s="45" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="57"/>
+      <c r="B80" s="61" t="s">
+        <v>121</v>
+      </c>
+      <c r="C80" s="74" t="s">
+        <v>122</v>
+      </c>
+      <c r="D80" s="105" t="s">
+        <v>194</v>
+      </c>
+      <c r="E80" s="43"/>
+      <c r="F80" s="43"/>
+      <c r="G80" s="43"/>
+      <c r="H80" s="43"/>
+      <c r="I80" s="44"/>
+    </row>
+    <row r="81" spans="1:9" s="114" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="111" t="s">
         <v>206</v>
       </c>
-      <c r="B80" s="135"/>
-      <c r="C80" s="112"/>
-      <c r="D80" s="113"/>
-      <c r="E80" s="113"/>
-      <c r="F80" s="113"/>
-      <c r="G80" s="113"/>
-      <c r="H80" s="113"/>
-      <c r="I80" s="113"/>
-    </row>
-    <row r="81" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="115"/>
-      <c r="B81" s="120" t="s">
-        <v>207</v>
-      </c>
-      <c r="C81" s="116" t="s">
-        <v>208</v>
-      </c>
-      <c r="D81" s="117" t="s">
-        <v>214</v>
-      </c>
-      <c r="E81" s="117"/>
-      <c r="F81" s="117"/>
-      <c r="G81" s="117"/>
-      <c r="H81" s="117"/>
-      <c r="I81" s="118"/>
-    </row>
-    <row r="82" spans="1:9" s="119" customFormat="1" ht="26" x14ac:dyDescent="0.3">
+      <c r="B81" s="135"/>
+      <c r="C81" s="112"/>
+      <c r="D81" s="113"/>
+      <c r="E81" s="113"/>
+      <c r="F81" s="113"/>
+      <c r="G81" s="113"/>
+      <c r="H81" s="113"/>
+      <c r="I81" s="113"/>
+    </row>
+    <row r="82" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="115"/>
       <c r="B82" s="120" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="C82" s="116" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="D82" s="117" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="E82" s="117"/>
       <c r="F82" s="117"/>
@@ -3461,16 +3484,16 @@
       <c r="H82" s="117"/>
       <c r="I82" s="118"/>
     </row>
-    <row r="83" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" s="119" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A83" s="115"/>
       <c r="B83" s="120" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="C83" s="116" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="D83" s="117" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="E83" s="117"/>
       <c r="F83" s="117"/>
@@ -3480,14 +3503,14 @@
     </row>
     <row r="84" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A84" s="115"/>
-      <c r="B84" s="137" t="s">
-        <v>233</v>
-      </c>
-      <c r="C84" s="119" t="s">
-        <v>234</v>
-      </c>
-      <c r="D84" s="117">
-        <v>90876</v>
+      <c r="B84" s="120" t="s">
+        <v>231</v>
+      </c>
+      <c r="C84" s="116" t="s">
+        <v>232</v>
+      </c>
+      <c r="D84" s="117" t="s">
+        <v>235</v>
       </c>
       <c r="E84" s="117"/>
       <c r="F84" s="117"/>
@@ -3497,12 +3520,14 @@
     </row>
     <row r="85" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="115"/>
-      <c r="B85" s="120" t="s">
-        <v>217</v>
-      </c>
-      <c r="C85" s="116"/>
-      <c r="D85" s="117" t="s">
-        <v>219</v>
+      <c r="B85" s="137" t="s">
+        <v>233</v>
+      </c>
+      <c r="C85" s="119" t="s">
+        <v>234</v>
+      </c>
+      <c r="D85" s="117">
+        <v>90876</v>
       </c>
       <c r="E85" s="117"/>
       <c r="F85" s="117"/>
@@ -3513,11 +3538,11 @@
     <row r="86" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="115"/>
       <c r="B86" s="120" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C86" s="116"/>
       <c r="D86" s="117" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E86" s="117"/>
       <c r="F86" s="117"/>
@@ -3528,11 +3553,11 @@
     <row r="87" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="115"/>
       <c r="B87" s="120" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="C87" s="116"/>
       <c r="D87" s="117" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E87" s="117"/>
       <c r="F87" s="117"/>
@@ -3543,11 +3568,11 @@
     <row r="88" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A88" s="115"/>
       <c r="B88" s="120" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C88" s="116"/>
       <c r="D88" s="117" t="s">
-        <v>182</v>
+        <v>215</v>
       </c>
       <c r="E88" s="117"/>
       <c r="F88" s="117"/>
@@ -3558,11 +3583,11 @@
     <row r="89" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="115"/>
       <c r="B89" s="120" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C89" s="116"/>
       <c r="D89" s="117" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="E89" s="117"/>
       <c r="F89" s="117"/>
@@ -3570,14 +3595,14 @@
       <c r="H89" s="117"/>
       <c r="I89" s="118"/>
     </row>
-    <row r="90" spans="1:9" s="119" customFormat="1" ht="31" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A90" s="115"/>
       <c r="B90" s="120" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C90" s="116"/>
       <c r="D90" s="117" t="s">
-        <v>183</v>
+        <v>216</v>
       </c>
       <c r="E90" s="117"/>
       <c r="F90" s="117"/>
@@ -3585,14 +3610,14 @@
       <c r="H90" s="117"/>
       <c r="I90" s="118"/>
     </row>
-    <row r="91" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" s="119" customFormat="1" ht="31" x14ac:dyDescent="0.3">
       <c r="A91" s="115"/>
       <c r="B91" s="120" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C91" s="116"/>
-      <c r="D91" s="117">
-        <v>10203</v>
+      <c r="D91" s="117" t="s">
+        <v>183</v>
       </c>
       <c r="E91" s="117"/>
       <c r="F91" s="117"/>
@@ -3602,20 +3627,35 @@
     </row>
     <row r="92" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A92" s="115"/>
-      <c r="B92" s="136" t="s">
-        <v>222</v>
-      </c>
-      <c r="C92" s="116" t="s">
-        <v>223</v>
-      </c>
-      <c r="D92" s="121" t="e" vm="1">
-        <v>#VALUE!</v>
+      <c r="B92" s="120" t="s">
+        <v>213</v>
+      </c>
+      <c r="C92" s="116"/>
+      <c r="D92" s="117">
+        <v>10203</v>
       </c>
       <c r="E92" s="117"/>
       <c r="F92" s="117"/>
       <c r="G92" s="117"/>
       <c r="H92" s="117"/>
       <c r="I92" s="118"/>
+    </row>
+    <row r="93" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="115"/>
+      <c r="B93" s="136" t="s">
+        <v>222</v>
+      </c>
+      <c r="C93" s="116" t="s">
+        <v>223</v>
+      </c>
+      <c r="D93" s="121" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E93" s="117"/>
+      <c r="F93" s="117"/>
+      <c r="G93" s="117"/>
+      <c r="H93" s="117"/>
+      <c r="I93" s="118"/>
     </row>
   </sheetData>
   <sheetProtection deleteColumns="0" selectLockedCells="1"/>
@@ -3628,7 +3668,7 @@
           <x14:formula1>
             <xm:f>'Drop Down List Values'!$M$2:$M$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D79:H79</xm:sqref>
+          <xm:sqref>D80:H80</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3916,28 +3956,55 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">YVWEJ5DVYS2U-421999773-68</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">
-      <Url>https://cdcpartners.sharepoint.com/sites/NCHS/nvssmodcop/_layouts/15/DocIdRedir.aspx?ID=YVWEJ5DVYS2U-421999773-68</Url>
-      <Description>YVWEJ5DVYS2U-421999773-68</Description>
-    </_dlc_DocIdUrl>
-    <ShareFileCreator xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
-    <ShareFileCreated xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008D4902BA52C7D94A994657A564808B2B" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e4455a60d2ff5f5fcd8815d6d89b5b66">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b541edd5-2552-480e-ada6-0e2c8d317108" xmlns:ns3="780ae317-08c5-4e10-af93-dd385a8384a9" xmlns:ns4="3146657c-56f4-4c0a-bb9c-a675121ac670" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1d01ecd782f081d5d944fa263943fc4" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="b541edd5-2552-480e-ada6-0e2c8d317108"/>
@@ -4136,83 +4203,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">YVWEJ5DVYS2U-421999773-68</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">
+      <Url>https://cdcpartners.sharepoint.com/sites/NCHS/nvssmodcop/_layouts/15/DocIdRedir.aspx?ID=YVWEJ5DVYS2U-421999773-68</Url>
+      <Description>YVWEJ5DVYS2U-421999773-68</Description>
+    </_dlc_DocIdUrl>
+    <ShareFileCreator xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
+    <ShareFileCreated xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{448710E8-BE9E-4C9E-A40A-0AC1DAE48E99}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF0D7A6D-D78F-4048-9348-0B4289842B11}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E3EF86-6C9E-4C22-A476-13DA012C68C5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="780ae317-08c5-4e10-af93-dd385a8384a9"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="b541edd5-2552-480e-ada6-0e2c8d317108"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3146657c-56f4-4c0a-bb9c-a675121ac670"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0980278E-2A79-4F44-8623-FE545C304BE1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4232,10 +4254,28 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E3EF86-6C9E-4C22-A476-13DA012C68C5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="780ae317-08c5-4e10-af93-dd385a8384a9"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="b541edd5-2552-480e-ada6-0e2c8d317108"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3146657c-56f4-4c0a-bb9c-a675121ac670"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF0D7A6D-D78F-4048-9348-0B4289842B11}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{448710E8-BE9E-4C9E-A40A-0AC1DAE48E99}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/tests/DCR-JackReacher.xlsx
+++ b/tests/DCR-JackReacher.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mc142/Documents/workspace/mortality-reporting/mdi-import/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73613D4B-07B2-0048-BBC4-F098F71DF9BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7920E210-BEB6-344C-B95F-A1B8123C70BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="660" windowWidth="33600" windowHeight="20660" xr2:uid="{7A50F290-1C75-487E-9806-F93553E4E7CC}"/>
+    <workbookView xWindow="960" yWindow="660" windowWidth="33600" windowHeight="20620" xr2:uid="{7A50F290-1C75-487E-9806-F93553E4E7CC}"/>
   </bookViews>
   <sheets>
     <sheet name="DCR" sheetId="4" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="242">
   <si>
     <t>Sections</t>
   </si>
@@ -872,6 +872,15 @@
   </si>
   <si>
     <t>24-1021-001</t>
+  </si>
+  <si>
+    <t>Funeral Home: Email</t>
+  </si>
+  <si>
+    <t>Funeral Home Email Address</t>
+  </si>
+  <si>
+    <t>FultonFuneral@fultonFH.com</t>
   </si>
 </sst>
 </file>
@@ -2047,7 +2056,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54CD1DC7-E143-4CF5-BEA9-4DABBAFFC7B0}">
-  <dimension ref="A1:AU93"/>
+  <dimension ref="A1:AU94"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="21" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.33203125" style="46" customWidth="1"/>
@@ -3537,12 +3546,14 @@
     </row>
     <row r="86" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="115"/>
-      <c r="B86" s="120" t="s">
-        <v>217</v>
-      </c>
-      <c r="C86" s="116"/>
+      <c r="B86" s="137" t="s">
+        <v>239</v>
+      </c>
+      <c r="C86" s="121" t="s">
+        <v>240</v>
+      </c>
       <c r="D86" s="117" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="E86" s="117"/>
       <c r="F86" s="117"/>
@@ -3553,11 +3564,11 @@
     <row r="87" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="115"/>
       <c r="B87" s="120" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C87" s="116"/>
       <c r="D87" s="117" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E87" s="117"/>
       <c r="F87" s="117"/>
@@ -3568,11 +3579,11 @@
     <row r="88" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A88" s="115"/>
       <c r="B88" s="120" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="C88" s="116"/>
       <c r="D88" s="117" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E88" s="117"/>
       <c r="F88" s="117"/>
@@ -3583,11 +3594,11 @@
     <row r="89" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="115"/>
       <c r="B89" s="120" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C89" s="116"/>
       <c r="D89" s="117" t="s">
-        <v>182</v>
+        <v>215</v>
       </c>
       <c r="E89" s="117"/>
       <c r="F89" s="117"/>
@@ -3598,11 +3609,11 @@
     <row r="90" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A90" s="115"/>
       <c r="B90" s="120" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C90" s="116"/>
       <c r="D90" s="117" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="E90" s="117"/>
       <c r="F90" s="117"/>
@@ -3610,14 +3621,14 @@
       <c r="H90" s="117"/>
       <c r="I90" s="118"/>
     </row>
-    <row r="91" spans="1:9" s="119" customFormat="1" ht="31" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A91" s="115"/>
       <c r="B91" s="120" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C91" s="116"/>
       <c r="D91" s="117" t="s">
-        <v>183</v>
+        <v>216</v>
       </c>
       <c r="E91" s="117"/>
       <c r="F91" s="117"/>
@@ -3625,14 +3636,14 @@
       <c r="H91" s="117"/>
       <c r="I91" s="118"/>
     </row>
-    <row r="92" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" s="119" customFormat="1" ht="31" x14ac:dyDescent="0.3">
       <c r="A92" s="115"/>
       <c r="B92" s="120" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C92" s="116"/>
-      <c r="D92" s="117">
-        <v>10203</v>
+      <c r="D92" s="117" t="s">
+        <v>183</v>
       </c>
       <c r="E92" s="117"/>
       <c r="F92" s="117"/>
@@ -3642,20 +3653,35 @@
     </row>
     <row r="93" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A93" s="115"/>
-      <c r="B93" s="136" t="s">
-        <v>222</v>
-      </c>
-      <c r="C93" s="116" t="s">
-        <v>223</v>
-      </c>
-      <c r="D93" s="121" t="e" vm="1">
-        <v>#VALUE!</v>
+      <c r="B93" s="120" t="s">
+        <v>213</v>
+      </c>
+      <c r="C93" s="116"/>
+      <c r="D93" s="117">
+        <v>10203</v>
       </c>
       <c r="E93" s="117"/>
       <c r="F93" s="117"/>
       <c r="G93" s="117"/>
       <c r="H93" s="117"/>
       <c r="I93" s="118"/>
+    </row>
+    <row r="94" spans="1:9" s="119" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="115"/>
+      <c r="B94" s="136" t="s">
+        <v>222</v>
+      </c>
+      <c r="C94" s="116" t="s">
+        <v>223</v>
+      </c>
+      <c r="D94" s="121" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E94" s="117"/>
+      <c r="F94" s="117"/>
+      <c r="G94" s="117"/>
+      <c r="H94" s="117"/>
+      <c r="I94" s="118"/>
     </row>
   </sheetData>
   <sheetProtection deleteColumns="0" selectLockedCells="1"/>
@@ -3955,56 +3981,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008D4902BA52C7D94A994657A564808B2B" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e4455a60d2ff5f5fcd8815d6d89b5b66">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b541edd5-2552-480e-ada6-0e2c8d317108" xmlns:ns3="780ae317-08c5-4e10-af93-dd385a8384a9" xmlns:ns4="3146657c-56f4-4c0a-bb9c-a675121ac670" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1d01ecd782f081d5d944fa263943fc4" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="b541edd5-2552-480e-ada6-0e2c8d317108"/>
@@ -4203,7 +4179,66 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">YVWEJ5DVYS2U-421999773-68</_dlc_DocId>
@@ -4217,24 +4252,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF0D7A6D-D78F-4048-9348-0B4289842B11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0980278E-2A79-4F44-8623-FE545C304BE1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4254,7 +4272,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF0D7A6D-D78F-4048-9348-0B4289842B11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{448710E8-BE9E-4C9E-A40A-0AC1DAE48E99}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E3EF86-6C9E-4C22-A476-13DA012C68C5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -4270,12 +4304,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{448710E8-BE9E-4C9E-A40A-0AC1DAE48E99}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>